--- a/research/traditional_assets/database/data/nigeria/nigeria_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_telecom_wireless.xlsx
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1400,22 +1400,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1370509891548315</v>
+        <v>0.136671336187367</v>
       </c>
       <c r="C2">
-        <v>4980.414862995713</v>
+        <v>4954.498494894498</v>
       </c>
       <c r="D2">
-        <v>4865.014862995713</v>
+        <v>4885.340494894499</v>
       </c>
       <c r="E2">
-        <v>-1902.7</v>
+        <v>-1856.458</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>46.242</v>
       </c>
       <c r="G2">
         <v>115.4</v>
@@ -1436,28 +1436,28 @@
         <v>444.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.3259726</v>
       </c>
       <c r="N2">
-        <v>444.4</v>
+        <v>442.0740274</v>
       </c>
       <c r="O2">
-        <v>133.32</v>
+        <v>132.62220822</v>
       </c>
       <c r="P2">
-        <v>311.08</v>
+        <v>309.45181918</v>
       </c>
       <c r="Q2">
-        <v>619.0799999999999</v>
+        <v>617.45181918</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1370509891548315</v>
+        <v>0.1376961981690576</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6407409627425109</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>191.0598602924213</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1482,22 +1482,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.136671336187367</v>
+        <v>0.1362916832199025</v>
       </c>
       <c r="C3">
-        <v>4954.498494894498</v>
+        <v>4928.752676974061</v>
       </c>
       <c r="D3">
-        <v>4885.340494894499</v>
+        <v>4905.836676974061</v>
       </c>
       <c r="E3">
-        <v>-1856.458</v>
+        <v>-1810.216</v>
       </c>
       <c r="F3">
-        <v>46.242</v>
+        <v>92.48399999999999</v>
       </c>
       <c r="G3">
         <v>115.4</v>
@@ -1518,28 +1518,28 @@
         <v>444.4</v>
       </c>
       <c r="M3">
-        <v>2.3259726</v>
+        <v>4.651945199999999</v>
       </c>
       <c r="N3">
-        <v>442.0740274</v>
+        <v>439.7480548</v>
       </c>
       <c r="O3">
-        <v>132.62220822</v>
+        <v>131.92441644</v>
       </c>
       <c r="P3">
-        <v>309.45181918</v>
+        <v>307.82363836</v>
       </c>
       <c r="Q3">
-        <v>617.45181918</v>
+        <v>615.82363836</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1376961981690576</v>
+        <v>0.1383545747141863</v>
       </c>
       <c r="T3">
-        <v>0.6407409627425109</v>
+        <v>0.6453314553828785</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>191.0598602924213</v>
+        <v>95.52993014621067</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1564,22 +1564,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1362916832199025</v>
+        <v>0.1359120302524381</v>
       </c>
       <c r="C4">
-        <v>4928.752676974061</v>
+        <v>4903.179564880501</v>
       </c>
       <c r="D4">
-        <v>4905.836676974061</v>
+        <v>4926.505564880501</v>
       </c>
       <c r="E4">
-        <v>-1810.216</v>
+        <v>-1763.974</v>
       </c>
       <c r="F4">
-        <v>92.48399999999999</v>
+        <v>138.726</v>
       </c>
       <c r="G4">
         <v>115.4</v>
@@ -1600,28 +1600,28 @@
         <v>444.4</v>
       </c>
       <c r="M4">
-        <v>4.651945199999999</v>
+        <v>6.977917799999999</v>
       </c>
       <c r="N4">
-        <v>439.7480548</v>
+        <v>437.4220822</v>
       </c>
       <c r="O4">
-        <v>131.92441644</v>
+        <v>131.22662466</v>
       </c>
       <c r="P4">
-        <v>307.82363836</v>
+        <v>306.19545754</v>
       </c>
       <c r="Q4">
-        <v>615.82363836</v>
+        <v>614.19545754</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1383545747141863</v>
+        <v>0.1390265260334413</v>
       </c>
       <c r="T4">
-        <v>0.6453314553828785</v>
+        <v>0.6500165973560371</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.52993014621067</v>
+        <v>63.68662009747378</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1359120302524381</v>
+        <v>0.1355323772849736</v>
       </c>
       <c r="C5">
-        <v>4903.179564880501</v>
+        <v>4877.781350741619</v>
       </c>
       <c r="D5">
-        <v>4926.505564880501</v>
+        <v>4947.34935074162</v>
       </c>
       <c r="E5">
-        <v>-1763.974</v>
+        <v>-1717.732</v>
       </c>
       <c r="F5">
-        <v>138.726</v>
+        <v>184.968</v>
       </c>
       <c r="G5">
         <v>115.4</v>
@@ -1682,28 +1682,28 @@
         <v>444.4</v>
       </c>
       <c r="M5">
-        <v>6.977917799999999</v>
+        <v>9.303890399999998</v>
       </c>
       <c r="N5">
-        <v>437.4220822</v>
+        <v>435.0961096</v>
       </c>
       <c r="O5">
-        <v>131.22662466</v>
+        <v>130.52883288</v>
       </c>
       <c r="P5">
-        <v>306.19545754</v>
+        <v>304.56727672</v>
       </c>
       <c r="Q5">
-        <v>614.19545754</v>
+        <v>612.56727672</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1390265260334413</v>
+        <v>0.1397124763385141</v>
       </c>
       <c r="T5">
-        <v>0.6500165973560371</v>
+        <v>0.6547993464536367</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.68662009747378</v>
+        <v>47.76496507310534</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1728,22 +1728,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1355323772849736</v>
+        <v>0.135152724317509</v>
       </c>
       <c r="C6">
-        <v>4877.781350741619</v>
+        <v>4852.560263941965</v>
       </c>
       <c r="D6">
-        <v>4947.34935074162</v>
+        <v>4968.370263941965</v>
       </c>
       <c r="E6">
-        <v>-1717.732</v>
+        <v>-1671.49</v>
       </c>
       <c r="F6">
-        <v>184.968</v>
+        <v>231.21</v>
       </c>
       <c r="G6">
         <v>115.4</v>
@@ -1764,28 +1764,28 @@
         <v>444.4</v>
       </c>
       <c r="M6">
-        <v>9.303890399999998</v>
+        <v>11.629863</v>
       </c>
       <c r="N6">
-        <v>435.0961096</v>
+        <v>432.770137</v>
       </c>
       <c r="O6">
-        <v>130.52883288</v>
+        <v>129.8310411</v>
       </c>
       <c r="P6">
-        <v>304.56727672</v>
+        <v>302.9390959</v>
       </c>
       <c r="Q6">
-        <v>612.56727672</v>
+        <v>610.9390959</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1397124763385141</v>
+        <v>0.1404128677026411</v>
       </c>
       <c r="T6">
-        <v>0.6547993464536367</v>
+        <v>0.6596827850059225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.76496507310534</v>
+        <v>38.21197205848426</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1810,22 +1810,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.135152724317509</v>
+        <v>0.1347730713500445</v>
       </c>
       <c r="C7">
-        <v>4852.560263941965</v>
+        <v>4827.5185719177</v>
       </c>
       <c r="D7">
-        <v>4968.370263941965</v>
+        <v>4989.5705719177</v>
       </c>
       <c r="E7">
-        <v>-1671.49</v>
+        <v>-1625.248</v>
       </c>
       <c r="F7">
-        <v>231.21</v>
+        <v>277.452</v>
       </c>
       <c r="G7">
         <v>115.4</v>
@@ -1846,28 +1846,28 @@
         <v>444.4</v>
       </c>
       <c r="M7">
-        <v>11.629863</v>
+        <v>13.9558356</v>
       </c>
       <c r="N7">
-        <v>432.770137</v>
+        <v>430.4441644</v>
       </c>
       <c r="O7">
-        <v>129.8310411</v>
+        <v>129.13324932</v>
       </c>
       <c r="P7">
-        <v>302.9390959</v>
+        <v>301.31091508</v>
       </c>
       <c r="Q7">
-        <v>610.9390959</v>
+        <v>609.31091508</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1404128677026411</v>
+        <v>0.1411281610106857</v>
       </c>
       <c r="T7">
-        <v>0.6596827850059225</v>
+        <v>0.6646701265061292</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.21197205848426</v>
+        <v>31.84331004873689</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1892,22 +1892,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1347730713500445</v>
+        <v>0.1343934183825801</v>
       </c>
       <c r="C8">
-        <v>4827.5185719177</v>
+        <v>4802.658580971934</v>
       </c>
       <c r="D8">
-        <v>4989.5705719177</v>
+        <v>5010.952580971935</v>
       </c>
       <c r="E8">
-        <v>-1625.248</v>
+        <v>-1579.006</v>
       </c>
       <c r="F8">
-        <v>277.452</v>
+        <v>323.694</v>
       </c>
       <c r="G8">
         <v>115.4</v>
@@ -1928,28 +1928,28 @@
         <v>444.4</v>
       </c>
       <c r="M8">
-        <v>13.9558356</v>
+        <v>16.2818082</v>
       </c>
       <c r="N8">
-        <v>430.4441644</v>
+        <v>428.1181918</v>
       </c>
       <c r="O8">
-        <v>129.13324932</v>
+        <v>128.43545754</v>
       </c>
       <c r="P8">
-        <v>301.31091508</v>
+        <v>299.68273426</v>
       </c>
       <c r="Q8">
-        <v>609.31091508</v>
+        <v>607.68273426</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1411281610106857</v>
+        <v>0.1418588369705162</v>
       </c>
       <c r="T8">
-        <v>0.6646701265061292</v>
+        <v>0.6697647226622545</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.84331004873689</v>
+        <v>27.2942657560602</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1974,22 +1974,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1343934183825801</v>
+        <v>0.1340137654151156</v>
       </c>
       <c r="C9">
-        <v>4802.658580971934</v>
+        <v>4777.982637111102</v>
       </c>
       <c r="D9">
-        <v>5010.952580971935</v>
+        <v>5032.518637111102</v>
       </c>
       <c r="E9">
-        <v>-1579.006</v>
+        <v>-1532.764</v>
       </c>
       <c r="F9">
-        <v>323.694</v>
+        <v>369.936</v>
       </c>
       <c r="G9">
         <v>115.4</v>
@@ -2010,28 +2010,28 @@
         <v>444.4</v>
       </c>
       <c r="M9">
-        <v>16.2818082</v>
+        <v>18.6077808</v>
       </c>
       <c r="N9">
-        <v>428.1181918</v>
+        <v>425.7922192</v>
       </c>
       <c r="O9">
-        <v>128.43545754</v>
+        <v>127.73766576</v>
       </c>
       <c r="P9">
-        <v>299.68273426</v>
+        <v>298.05455344</v>
       </c>
       <c r="Q9">
-        <v>607.68273426</v>
+        <v>606.0545534400001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1418588369705162</v>
+        <v>0.142605397190343</v>
       </c>
       <c r="T9">
-        <v>0.6697647226622545</v>
+        <v>0.6749700709087303</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.29426575606019</v>
+        <v>23.88248253655267</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2056,22 +2056,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1340137654151156</v>
+        <v>0.1336341124476511</v>
       </c>
       <c r="C10">
-        <v>4777.982637111102</v>
+        <v>4753.49312690302</v>
       </c>
       <c r="D10">
-        <v>5032.518637111102</v>
+        <v>5054.271126903021</v>
       </c>
       <c r="E10">
-        <v>-1532.764</v>
+        <v>-1486.522</v>
       </c>
       <c r="F10">
-        <v>369.936</v>
+        <v>416.1779999999999</v>
       </c>
       <c r="G10">
         <v>115.4</v>
@@ -2092,28 +2092,28 @@
         <v>444.4</v>
       </c>
       <c r="M10">
-        <v>18.6077808</v>
+        <v>20.9337534</v>
       </c>
       <c r="N10">
-        <v>425.7922192</v>
+        <v>423.4662466</v>
       </c>
       <c r="O10">
-        <v>127.73766576</v>
+        <v>127.03987398</v>
       </c>
       <c r="P10">
-        <v>298.05455344</v>
+        <v>296.42637262</v>
       </c>
       <c r="Q10">
-        <v>606.0545534400001</v>
+        <v>604.4263726199999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.142605397190343</v>
+        <v>0.1433683653270891</v>
       </c>
       <c r="T10">
-        <v>0.6749700709087303</v>
+        <v>0.6802898224133703</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.88248253655267</v>
+        <v>21.22887336582459</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2138,22 +2138,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1336341124476511</v>
+        <v>0.1332544594801866</v>
       </c>
       <c r="C11">
-        <v>4753.49312690302</v>
+        <v>4729.192478357301</v>
       </c>
       <c r="D11">
-        <v>5054.271126903021</v>
+        <v>5076.212478357302</v>
       </c>
       <c r="E11">
-        <v>-1486.522</v>
+        <v>-1440.28</v>
       </c>
       <c r="F11">
-        <v>416.1779999999999</v>
+        <v>462.42</v>
       </c>
       <c r="G11">
         <v>115.4</v>
@@ -2174,28 +2174,28 @@
         <v>444.4</v>
       </c>
       <c r="M11">
-        <v>20.9337534</v>
+        <v>23.259726</v>
       </c>
       <c r="N11">
-        <v>423.4662466</v>
+        <v>421.140274</v>
       </c>
       <c r="O11">
-        <v>127.03987398</v>
+        <v>126.3420822</v>
       </c>
       <c r="P11">
-        <v>296.42637262</v>
+        <v>294.7981918</v>
       </c>
       <c r="Q11">
-        <v>604.4263726199999</v>
+        <v>602.7981918</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1433683653270891</v>
+        <v>0.1441482883113184</v>
       </c>
       <c r="T11">
-        <v>0.6802898224133703</v>
+        <v>0.6857277906181134</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.22887336582459</v>
+        <v>19.10598602924214</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2220,22 +2220,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1332544594801866</v>
+        <v>0.1328748065127221</v>
       </c>
       <c r="C12">
-        <v>4729.192478357301</v>
+        <v>4705.083161828805</v>
       </c>
       <c r="D12">
-        <v>5076.212478357302</v>
+        <v>5098.345161828805</v>
       </c>
       <c r="E12">
-        <v>-1440.28</v>
+        <v>-1394.038</v>
       </c>
       <c r="F12">
-        <v>462.42</v>
+        <v>508.662</v>
       </c>
       <c r="G12">
         <v>115.4</v>
@@ -2256,28 +2256,28 @@
         <v>444.4</v>
       </c>
       <c r="M12">
-        <v>23.259726</v>
+        <v>25.5856986</v>
       </c>
       <c r="N12">
-        <v>421.140274</v>
+        <v>418.8143014</v>
       </c>
       <c r="O12">
-        <v>126.3420822</v>
+        <v>125.64429042</v>
       </c>
       <c r="P12">
-        <v>294.7981918</v>
+        <v>293.17001098</v>
       </c>
       <c r="Q12">
-        <v>602.7981918</v>
+        <v>601.1700109799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1441482883113184</v>
+        <v>0.1449457376547439</v>
       </c>
       <c r="T12">
-        <v>0.6857277906181134</v>
+        <v>0.6912879603555475</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.10598602924213</v>
+        <v>17.36907820840194</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2302,22 +2302,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1328748065127221</v>
+        <v>0.1324951535452576</v>
       </c>
       <c r="C13">
-        <v>4705.083161828805</v>
+        <v>4681.167690944831</v>
       </c>
       <c r="D13">
-        <v>5098.345161828805</v>
+        <v>5120.671690944831</v>
       </c>
       <c r="E13">
-        <v>-1394.038</v>
+        <v>-1347.796</v>
       </c>
       <c r="F13">
-        <v>508.662</v>
+        <v>554.904</v>
       </c>
       <c r="G13">
         <v>115.4</v>
@@ -2338,28 +2338,28 @@
         <v>444.4</v>
       </c>
       <c r="M13">
-        <v>25.5856986</v>
+        <v>27.9116712</v>
       </c>
       <c r="N13">
-        <v>418.8143014</v>
+        <v>416.4883288</v>
       </c>
       <c r="O13">
-        <v>125.64429042</v>
+        <v>124.94649864</v>
       </c>
       <c r="P13">
-        <v>293.17001098</v>
+        <v>291.54183016</v>
       </c>
       <c r="Q13">
-        <v>601.1700109799999</v>
+        <v>599.54183016</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1449457376547439</v>
+        <v>0.1457613108468837</v>
       </c>
       <c r="T13">
-        <v>0.6912879603555475</v>
+        <v>0.6969744975870141</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.36907820840194</v>
+        <v>15.92165502436844</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2384,22 +2384,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1324951535452576</v>
+        <v>0.1321155005777931</v>
       </c>
       <c r="C14">
-        <v>4681.167690944831</v>
+        <v>4657.448623556763</v>
       </c>
       <c r="D14">
-        <v>5120.671690944831</v>
+        <v>5143.194623556763</v>
       </c>
       <c r="E14">
-        <v>-1347.796</v>
+        <v>-1301.554</v>
       </c>
       <c r="F14">
-        <v>554.904</v>
+        <v>601.146</v>
       </c>
       <c r="G14">
         <v>115.4</v>
@@ -2420,28 +2420,28 @@
         <v>444.4</v>
       </c>
       <c r="M14">
-        <v>27.9116712</v>
+        <v>30.2376438</v>
       </c>
       <c r="N14">
-        <v>416.4883288</v>
+        <v>414.1623562</v>
       </c>
       <c r="O14">
-        <v>124.94649864</v>
+        <v>124.24870686</v>
       </c>
       <c r="P14">
-        <v>291.54183016</v>
+        <v>289.91364934</v>
       </c>
       <c r="Q14">
-        <v>599.54183016</v>
+        <v>597.91364934</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1457613108468837</v>
+        <v>0.146595632848038</v>
       </c>
       <c r="T14">
-        <v>0.6969744975870141</v>
+        <v>0.7027917598123075</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.92165502436844</v>
+        <v>14.69691233018626</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2466,22 +2466,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1321155005777931</v>
+        <v>0.1317358476103286</v>
       </c>
       <c r="C15">
-        <v>4657.448623556763</v>
+        <v>4633.928562716947</v>
       </c>
       <c r="D15">
-        <v>5143.194623556763</v>
+        <v>5165.916562716947</v>
       </c>
       <c r="E15">
-        <v>-1301.554</v>
+        <v>-1255.312</v>
       </c>
       <c r="F15">
-        <v>601.146</v>
+        <v>647.388</v>
       </c>
       <c r="G15">
         <v>115.4</v>
@@ -2502,28 +2502,28 @@
         <v>444.4</v>
       </c>
       <c r="M15">
-        <v>30.2376438</v>
+        <v>32.5636164</v>
       </c>
       <c r="N15">
-        <v>414.1623562</v>
+        <v>411.8363836</v>
       </c>
       <c r="O15">
-        <v>124.24870686</v>
+        <v>123.55091508</v>
       </c>
       <c r="P15">
-        <v>289.91364934</v>
+        <v>288.28546852</v>
       </c>
       <c r="Q15">
-        <v>597.91364934</v>
+        <v>596.28546852</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.146595632848038</v>
+        <v>0.1474493576864286</v>
       </c>
       <c r="T15">
-        <v>0.7027917598123075</v>
+        <v>0.708744307205631</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.69691233018626</v>
+        <v>13.64713287803009</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2548,22 +2548,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1317358476103286</v>
+        <v>0.1315136946428641</v>
       </c>
       <c r="C16">
-        <v>4633.928562716947</v>
+        <v>4601.075598143119</v>
       </c>
       <c r="D16">
-        <v>5165.916562716947</v>
+        <v>5179.30559814312</v>
       </c>
       <c r="E16">
-        <v>-1255.312</v>
+        <v>-1209.07</v>
       </c>
       <c r="F16">
-        <v>647.388</v>
+        <v>693.6300000000001</v>
       </c>
       <c r="G16">
         <v>115.4</v>
@@ -2584,45 +2584,45 @@
         <v>444.4</v>
       </c>
       <c r="M16">
-        <v>32.5636164</v>
+        <v>35.93003400000001</v>
       </c>
       <c r="N16">
-        <v>411.8363836</v>
+        <v>408.469966</v>
       </c>
       <c r="O16">
-        <v>123.55091508</v>
+        <v>122.5409898</v>
       </c>
       <c r="P16">
-        <v>288.28546852</v>
+        <v>285.9289762</v>
       </c>
       <c r="Q16">
-        <v>596.28546852</v>
+        <v>593.9289762000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1474493576864286</v>
+        <v>0.1483231701680754</v>
       </c>
       <c r="T16">
-        <v>0.708744307205631</v>
+        <v>0.714836914537621</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.64713287803009</v>
+        <v>12.36848259035881</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2630,22 +2630,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1315136946428641</v>
+        <v>0.1311445416753996</v>
       </c>
       <c r="C17">
-        <v>4601.075598143119</v>
+        <v>4577.236390324393</v>
       </c>
       <c r="D17">
-        <v>5179.30559814312</v>
+        <v>5201.708390324394</v>
       </c>
       <c r="E17">
-        <v>-1209.07</v>
+        <v>-1162.828</v>
       </c>
       <c r="F17">
-        <v>693.63</v>
+        <v>739.872</v>
       </c>
       <c r="G17">
         <v>115.4</v>
@@ -2666,28 +2666,28 @@
         <v>444.4</v>
       </c>
       <c r="M17">
-        <v>35.930034</v>
+        <v>38.32536959999999</v>
       </c>
       <c r="N17">
-        <v>408.469966</v>
+        <v>406.0746304</v>
       </c>
       <c r="O17">
-        <v>122.5409898</v>
+        <v>121.82238912</v>
       </c>
       <c r="P17">
-        <v>285.9289762</v>
+        <v>284.25224128</v>
       </c>
       <c r="Q17">
-        <v>593.9289762000001</v>
+        <v>592.25224128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1483231701680754</v>
+        <v>0.1492177877088091</v>
       </c>
       <c r="T17">
-        <v>0.714836914537621</v>
+        <v>0.7210745839489441</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.36848259035881</v>
+        <v>11.59545242846138</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2712,22 +2712,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1311445416753996</v>
+        <v>0.1307753887079351</v>
       </c>
       <c r="C18">
-        <v>4577.236390324393</v>
+        <v>4553.591828445838</v>
       </c>
       <c r="D18">
-        <v>5201.708390324394</v>
+        <v>5224.305828445838</v>
       </c>
       <c r="E18">
-        <v>-1162.828</v>
+        <v>-1116.586</v>
       </c>
       <c r="F18">
-        <v>739.872</v>
+        <v>786.114</v>
       </c>
       <c r="G18">
         <v>115.4</v>
@@ -2748,28 +2748,28 @@
         <v>444.4</v>
       </c>
       <c r="M18">
-        <v>38.32536959999999</v>
+        <v>40.7207052</v>
       </c>
       <c r="N18">
-        <v>406.0746304</v>
+        <v>403.6792948</v>
       </c>
       <c r="O18">
-        <v>121.82238912</v>
+        <v>121.10378844</v>
       </c>
       <c r="P18">
-        <v>284.25224128</v>
+        <v>282.57550636</v>
       </c>
       <c r="Q18">
-        <v>592.25224128</v>
+        <v>590.57550636</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1492177877088091</v>
+        <v>0.150133962298717</v>
       </c>
       <c r="T18">
-        <v>0.7210745839489441</v>
+        <v>0.727462558647287</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.59545242846138</v>
+        <v>10.91336699149307</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2794,22 +2794,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1307753887079351</v>
+        <v>0.1304062357404706</v>
       </c>
       <c r="C19">
-        <v>4553.591828445838</v>
+        <v>4530.144460338324</v>
       </c>
       <c r="D19">
-        <v>5224.305828445838</v>
+        <v>5247.100460338324</v>
       </c>
       <c r="E19">
-        <v>-1116.586</v>
+        <v>-1070.344</v>
       </c>
       <c r="F19">
-        <v>786.114</v>
+        <v>832.3560000000001</v>
       </c>
       <c r="G19">
         <v>115.4</v>
@@ -2830,28 +2830,28 @@
         <v>444.4</v>
       </c>
       <c r="M19">
-        <v>40.7207052</v>
+        <v>43.11604080000001</v>
       </c>
       <c r="N19">
-        <v>403.6792948</v>
+        <v>401.2839592</v>
       </c>
       <c r="O19">
-        <v>121.10378844</v>
+        <v>120.38518776</v>
       </c>
       <c r="P19">
-        <v>282.57550636</v>
+        <v>280.89877144</v>
       </c>
       <c r="Q19">
-        <v>590.57550636</v>
+        <v>588.89877144</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.150133962298717</v>
+        <v>0.15107248261033</v>
       </c>
       <c r="T19">
-        <v>0.727462558647287</v>
+        <v>0.734006337606565</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.91336699149307</v>
+        <v>10.307068825299</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2876,22 +2876,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1304062357404706</v>
+        <v>0.1302631827730061</v>
       </c>
       <c r="C20">
-        <v>4530.144460338322</v>
+        <v>4492.789329939874</v>
       </c>
       <c r="D20">
-        <v>5247.100460338322</v>
+        <v>5255.987329939874</v>
       </c>
       <c r="E20">
-        <v>-1070.344</v>
+        <v>-1024.102</v>
       </c>
       <c r="F20">
-        <v>832.3559999999999</v>
+        <v>878.598</v>
       </c>
       <c r="G20">
         <v>115.4</v>
@@ -2912,45 +2912,45 @@
         <v>444.4</v>
       </c>
       <c r="M20">
-        <v>43.11604079999999</v>
+        <v>47.004993</v>
       </c>
       <c r="N20">
-        <v>401.2839592</v>
+        <v>397.395007</v>
       </c>
       <c r="O20">
-        <v>120.38518776</v>
+        <v>119.2185021</v>
       </c>
       <c r="P20">
-        <v>280.89877144</v>
+        <v>278.1765049</v>
       </c>
       <c r="Q20">
-        <v>588.89877144</v>
+        <v>586.1765049000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.15107248261033</v>
+        <v>0.1520341762629705</v>
       </c>
       <c r="T20">
-        <v>0.734006337606565</v>
+        <v>0.740711691354961</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.30706882529901</v>
+        <v>9.454314778857642</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2958,22 +2958,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1302631827730061</v>
+        <v>0.1299059298055417</v>
       </c>
       <c r="C21">
-        <v>4492.789329939874</v>
+        <v>4468.872950439143</v>
       </c>
       <c r="D21">
-        <v>5255.987329939874</v>
+        <v>5278.312950439144</v>
       </c>
       <c r="E21">
-        <v>-1024.102</v>
+        <v>-977.86</v>
       </c>
       <c r="F21">
-        <v>878.598</v>
+        <v>924.84</v>
       </c>
       <c r="G21">
         <v>115.4</v>
@@ -2994,28 +2994,28 @@
         <v>444.4</v>
       </c>
       <c r="M21">
-        <v>47.004993</v>
+        <v>49.47894</v>
       </c>
       <c r="N21">
-        <v>397.395007</v>
+        <v>394.92106</v>
       </c>
       <c r="O21">
-        <v>119.2185021</v>
+        <v>118.476318</v>
       </c>
       <c r="P21">
-        <v>278.1765049</v>
+        <v>276.444742</v>
       </c>
       <c r="Q21">
-        <v>586.1765049000001</v>
+        <v>584.4447419999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1520341762629705</v>
+        <v>0.1530199122569271</v>
       </c>
       <c r="T21">
-        <v>0.740711691354961</v>
+        <v>0.747584678947067</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.454314778857642</v>
+        <v>8.981599039914759</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3040,22 +3040,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1299059298055417</v>
+        <v>0.1295486768380772</v>
       </c>
       <c r="C22">
-        <v>4468.872950439143</v>
+        <v>4445.147043062272</v>
       </c>
       <c r="D22">
-        <v>5278.312950439144</v>
+        <v>5300.829043062273</v>
       </c>
       <c r="E22">
-        <v>-977.86</v>
+        <v>-931.6179999999999</v>
       </c>
       <c r="F22">
-        <v>924.84</v>
+        <v>971.0820000000001</v>
       </c>
       <c r="G22">
         <v>115.4</v>
@@ -3076,28 +3076,28 @@
         <v>444.4</v>
       </c>
       <c r="M22">
-        <v>49.47894</v>
+        <v>51.952887</v>
       </c>
       <c r="N22">
-        <v>394.92106</v>
+        <v>392.4471129999999</v>
       </c>
       <c r="O22">
-        <v>118.476318</v>
+        <v>117.7341339</v>
       </c>
       <c r="P22">
-        <v>276.444742</v>
+        <v>274.7129791</v>
       </c>
       <c r="Q22">
-        <v>584.4447419999999</v>
+        <v>582.7129791</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1530199122569271</v>
+        <v>0.1540306035925027</v>
       </c>
       <c r="T22">
-        <v>0.747584678947067</v>
+        <v>0.7546316662250491</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.981599039914759</v>
+        <v>8.553903847537864</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3122,22 +3122,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1295486768380771</v>
+        <v>0.1291914238706127</v>
       </c>
       <c r="C23">
-        <v>4445.147043062274</v>
+        <v>4421.614055785143</v>
       </c>
       <c r="D23">
-        <v>5300.829043062275</v>
+        <v>5323.538055785143</v>
       </c>
       <c r="E23">
-        <v>-931.6180000000002</v>
+        <v>-885.3760000000001</v>
       </c>
       <c r="F23">
-        <v>971.0819999999999</v>
+        <v>1017.324</v>
       </c>
       <c r="G23">
         <v>115.4</v>
@@ -3158,28 +3158,28 @@
         <v>444.4</v>
       </c>
       <c r="M23">
-        <v>51.95288699999999</v>
+        <v>54.426834</v>
       </c>
       <c r="N23">
-        <v>392.447113</v>
+        <v>389.973166</v>
       </c>
       <c r="O23">
-        <v>117.7341339</v>
+        <v>116.9919498</v>
       </c>
       <c r="P23">
-        <v>274.7129791</v>
+        <v>272.9812162</v>
       </c>
       <c r="Q23">
-        <v>582.7129791</v>
+        <v>580.9812162000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1540306035925027</v>
+        <v>0.155067210090529</v>
       </c>
       <c r="T23">
-        <v>0.754631666225049</v>
+        <v>0.7618593454845178</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.553903847537867</v>
+        <v>8.165090036286145</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3204,22 +3204,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1291914238706127</v>
+        <v>0.1288341709031482</v>
       </c>
       <c r="C24">
-        <v>4421.614055785143</v>
+        <v>4398.276478713117</v>
       </c>
       <c r="D24">
-        <v>5323.538055785143</v>
+        <v>5346.442478713117</v>
       </c>
       <c r="E24">
-        <v>-885.3760000000001</v>
+        <v>-839.134</v>
       </c>
       <c r="F24">
-        <v>1017.324</v>
+        <v>1063.566</v>
       </c>
       <c r="G24">
         <v>115.4</v>
@@ -3240,28 +3240,28 @@
         <v>444.4</v>
       </c>
       <c r="M24">
-        <v>54.426834</v>
+        <v>56.900781</v>
       </c>
       <c r="N24">
-        <v>389.973166</v>
+        <v>387.499219</v>
       </c>
       <c r="O24">
-        <v>116.9919498</v>
+        <v>116.2497657</v>
       </c>
       <c r="P24">
-        <v>272.9812162</v>
+        <v>271.2494533</v>
       </c>
       <c r="Q24">
-        <v>580.9812162000001</v>
+        <v>579.2494533</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.155067210090529</v>
+        <v>0.15613074143266</v>
       </c>
       <c r="T24">
-        <v>0.7618593454845178</v>
+        <v>0.7692747566728039</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.165090036286145</v>
+        <v>7.810086121665008</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3286,22 +3286,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1288341709031482</v>
+        <v>0.1286113179356837</v>
       </c>
       <c r="C25">
-        <v>4398.276478713117</v>
+        <v>4366.422253252399</v>
       </c>
       <c r="D25">
-        <v>5346.442478713117</v>
+        <v>5360.830253252399</v>
       </c>
       <c r="E25">
-        <v>-839.134</v>
+        <v>-792.8920000000001</v>
       </c>
       <c r="F25">
-        <v>1063.566</v>
+        <v>1109.808</v>
       </c>
       <c r="G25">
         <v>115.4</v>
@@ -3322,45 +3322,45 @@
         <v>444.4</v>
       </c>
       <c r="M25">
-        <v>56.900781</v>
+        <v>60.2625744</v>
       </c>
       <c r="N25">
-        <v>387.499219</v>
+        <v>384.1374256</v>
       </c>
       <c r="O25">
-        <v>116.2497657</v>
+        <v>115.24122768</v>
       </c>
       <c r="P25">
-        <v>271.2494533</v>
+        <v>268.89619792</v>
       </c>
       <c r="Q25">
-        <v>579.2494533</v>
+        <v>576.89619792</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.15613074143266</v>
+        <v>0.157222260441689</v>
       </c>
       <c r="T25">
-        <v>0.7692747566728039</v>
+        <v>0.7768853102607819</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.810086121665008</v>
+        <v>7.374394546277465</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3368,22 +3368,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1286113179356837</v>
+        <v>0.1282596649682192</v>
       </c>
       <c r="C26">
-        <v>4366.422253252399</v>
+        <v>4343.041756113903</v>
       </c>
       <c r="D26">
-        <v>5360.830253252399</v>
+        <v>5383.691756113903</v>
       </c>
       <c r="E26">
-        <v>-792.8920000000001</v>
+        <v>-746.6500000000001</v>
       </c>
       <c r="F26">
-        <v>1109.808</v>
+        <v>1156.05</v>
       </c>
       <c r="G26">
         <v>115.4</v>
@@ -3404,28 +3404,28 @@
         <v>444.4</v>
       </c>
       <c r="M26">
-        <v>60.2625744</v>
+        <v>62.773515</v>
       </c>
       <c r="N26">
-        <v>384.1374256</v>
+        <v>381.626485</v>
       </c>
       <c r="O26">
-        <v>115.24122768</v>
+        <v>114.4879455</v>
       </c>
       <c r="P26">
-        <v>268.89619792</v>
+        <v>267.1385395</v>
       </c>
       <c r="Q26">
-        <v>576.89619792</v>
+        <v>575.1385395</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.157222260441689</v>
+        <v>0.1583428866242922</v>
       </c>
       <c r="T26">
-        <v>0.7768853102607819</v>
+        <v>0.7846988119444391</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.374394546277465</v>
+        <v>7.079418764426367</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3450,22 +3450,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1282596649682192</v>
+        <v>0.1279080120007547</v>
       </c>
       <c r="C27">
-        <v>4343.041756113903</v>
+        <v>4319.857081895147</v>
       </c>
       <c r="D27">
-        <v>5383.691756113903</v>
+        <v>5406.749081895146</v>
       </c>
       <c r="E27">
-        <v>-746.6500000000001</v>
+        <v>-700.4080000000001</v>
       </c>
       <c r="F27">
-        <v>1156.05</v>
+        <v>1202.292</v>
       </c>
       <c r="G27">
         <v>115.4</v>
@@ -3486,28 +3486,28 @@
         <v>444.4</v>
       </c>
       <c r="M27">
-        <v>62.773515</v>
+        <v>65.2844556</v>
       </c>
       <c r="N27">
-        <v>381.626485</v>
+        <v>379.1155444</v>
       </c>
       <c r="O27">
-        <v>114.4879455</v>
+        <v>113.73466332</v>
       </c>
       <c r="P27">
-        <v>267.1385395</v>
+        <v>265.38088108</v>
       </c>
       <c r="Q27">
-        <v>575.1385395</v>
+        <v>573.38088108</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1583428866242922</v>
+        <v>0.1594938000010198</v>
       </c>
       <c r="T27">
-        <v>0.7846988119444391</v>
+        <v>0.7927234893492763</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.079418764426367</v>
+        <v>6.807133427333045</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1279080120007547</v>
+        <v>0.1275563590332902</v>
       </c>
       <c r="C28">
-        <v>4319.857081895147</v>
+        <v>4296.870757434834</v>
       </c>
       <c r="D28">
-        <v>5406.749081895146</v>
+        <v>5430.004757434835</v>
       </c>
       <c r="E28">
-        <v>-700.4080000000001</v>
+        <v>-654.1659999999999</v>
       </c>
       <c r="F28">
-        <v>1202.292</v>
+        <v>1248.534</v>
       </c>
       <c r="G28">
         <v>115.4</v>
@@ -3568,28 +3568,28 @@
         <v>444.4</v>
       </c>
       <c r="M28">
-        <v>65.2844556</v>
+        <v>67.79539620000001</v>
       </c>
       <c r="N28">
-        <v>379.1155444</v>
+        <v>376.6046037999999</v>
       </c>
       <c r="O28">
-        <v>113.73466332</v>
+        <v>112.98138114</v>
       </c>
       <c r="P28">
-        <v>265.38088108</v>
+        <v>263.62322266</v>
       </c>
       <c r="Q28">
-        <v>573.38088108</v>
+        <v>571.62322266</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1594938000010198</v>
+        <v>0.1606762452510825</v>
       </c>
       <c r="T28">
-        <v>0.7927234893492763</v>
+        <v>0.8009680209295886</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.807133427333045</v>
+        <v>6.555017374468856</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3614,22 +3614,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1275563590332902</v>
+        <v>0.1272047060658257</v>
       </c>
       <c r="C29">
-        <v>4296.870757434834</v>
+        <v>4274.085353233537</v>
       </c>
       <c r="D29">
-        <v>5430.004757434835</v>
+        <v>5453.461353233537</v>
       </c>
       <c r="E29">
-        <v>-654.1659999999999</v>
+        <v>-607.924</v>
       </c>
       <c r="F29">
-        <v>1248.534</v>
+        <v>1294.776</v>
       </c>
       <c r="G29">
         <v>115.4</v>
@@ -3650,28 +3650,28 @@
         <v>444.4</v>
       </c>
       <c r="M29">
-        <v>67.79539620000001</v>
+        <v>70.30633680000001</v>
       </c>
       <c r="N29">
-        <v>376.6046037999999</v>
+        <v>374.0936632</v>
       </c>
       <c r="O29">
-        <v>112.98138114</v>
+        <v>112.22809896</v>
       </c>
       <c r="P29">
-        <v>263.62322266</v>
+        <v>261.86556424</v>
       </c>
       <c r="Q29">
-        <v>571.62322266</v>
+        <v>569.8655642399999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1606762452510825</v>
+        <v>0.1618915362025357</v>
       </c>
       <c r="T29">
-        <v>0.8009680209295886</v>
+        <v>0.8094415672760205</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.555017374468856</v>
+        <v>6.32090961109497</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3696,22 +3696,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1272047060658257</v>
+        <v>0.1270560530983612</v>
       </c>
       <c r="C30">
-        <v>4274.085353233537</v>
+        <v>4237.820126436262</v>
       </c>
       <c r="D30">
-        <v>5453.461353233537</v>
+        <v>5463.438126436263</v>
       </c>
       <c r="E30">
-        <v>-607.924</v>
+        <v>-561.682</v>
       </c>
       <c r="F30">
-        <v>1294.776</v>
+        <v>1341.018</v>
       </c>
       <c r="G30">
         <v>115.4</v>
@@ -3732,45 +3732,45 @@
         <v>444.4</v>
       </c>
       <c r="M30">
-        <v>70.30633680000001</v>
+        <v>74.1582954</v>
       </c>
       <c r="N30">
-        <v>374.0936632</v>
+        <v>370.2417046</v>
       </c>
       <c r="O30">
-        <v>112.22809896</v>
+        <v>111.07251138</v>
       </c>
       <c r="P30">
-        <v>261.86556424</v>
+        <v>259.16919322</v>
       </c>
       <c r="Q30">
-        <v>569.8655642399999</v>
+        <v>567.16919322</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1618915362025357</v>
+        <v>0.1631410607019172</v>
       </c>
       <c r="T30">
-        <v>0.8094415672760205</v>
+        <v>0.818153805068831</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.32090961109497</v>
+        <v>5.992586501657912</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3778,22 +3778,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1270560530983612</v>
+        <v>0.1267114001308967</v>
       </c>
       <c r="C31">
-        <v>4237.820126436262</v>
+        <v>4214.850374349272</v>
       </c>
       <c r="D31">
-        <v>5463.438126436263</v>
+        <v>5486.710374349273</v>
       </c>
       <c r="E31">
-        <v>-561.6820000000002</v>
+        <v>-515.4400000000001</v>
       </c>
       <c r="F31">
-        <v>1341.018</v>
+        <v>1387.26</v>
       </c>
       <c r="G31">
         <v>115.4</v>
@@ -3814,28 +3814,28 @@
         <v>444.4</v>
       </c>
       <c r="M31">
-        <v>74.15829539999999</v>
+        <v>76.715478</v>
       </c>
       <c r="N31">
-        <v>370.2417046</v>
+        <v>367.684522</v>
       </c>
       <c r="O31">
-        <v>111.07251138</v>
+        <v>110.3053566</v>
       </c>
       <c r="P31">
-        <v>259.16919322</v>
+        <v>257.3791654</v>
       </c>
       <c r="Q31">
-        <v>567.16919322</v>
+        <v>565.3791653999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1631410607019172</v>
+        <v>0.164426285901281</v>
       </c>
       <c r="T31">
-        <v>0.818153805068831</v>
+        <v>0.8271149639414359</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.992586501657913</v>
+        <v>5.792833618269314</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3860,22 +3860,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1267114001308967</v>
+        <v>0.1263667471634322</v>
       </c>
       <c r="C32">
-        <v>4214.850374349272</v>
+        <v>4192.079732927294</v>
       </c>
       <c r="D32">
-        <v>5486.710374349273</v>
+        <v>5510.181732927294</v>
       </c>
       <c r="E32">
-        <v>-515.4400000000001</v>
+        <v>-469.1980000000001</v>
       </c>
       <c r="F32">
-        <v>1387.26</v>
+        <v>1433.502</v>
       </c>
       <c r="G32">
         <v>115.4</v>
@@ -3896,28 +3896,28 @@
         <v>444.4</v>
       </c>
       <c r="M32">
-        <v>76.715478</v>
+        <v>79.27266059999999</v>
       </c>
       <c r="N32">
-        <v>367.684522</v>
+        <v>365.1273394</v>
       </c>
       <c r="O32">
-        <v>110.3053566</v>
+        <v>109.53820182</v>
       </c>
       <c r="P32">
-        <v>257.3791654</v>
+        <v>255.58913758</v>
       </c>
       <c r="Q32">
-        <v>565.3791653999999</v>
+        <v>563.5891375799999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.164426285901281</v>
+        <v>0.1657487640049742</v>
       </c>
       <c r="T32">
-        <v>0.8271149639414359</v>
+        <v>0.8363358665494786</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.792833618269314</v>
+        <v>5.605968017679982</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3942,22 +3942,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1263667471634322</v>
+        <v>0.1260220941959677</v>
       </c>
       <c r="C33">
-        <v>4192.079732927294</v>
+        <v>4169.510768448943</v>
       </c>
       <c r="D33">
-        <v>5510.181732927294</v>
+        <v>5533.854768448943</v>
       </c>
       <c r="E33">
-        <v>-469.1980000000001</v>
+        <v>-422.9560000000001</v>
       </c>
       <c r="F33">
-        <v>1433.502</v>
+        <v>1479.744</v>
       </c>
       <c r="G33">
         <v>115.4</v>
@@ -3978,28 +3978,28 @@
         <v>444.4</v>
       </c>
       <c r="M33">
-        <v>79.27266059999999</v>
+        <v>81.8298432</v>
       </c>
       <c r="N33">
-        <v>365.1273394</v>
+        <v>362.5701567999999</v>
       </c>
       <c r="O33">
-        <v>109.53820182</v>
+        <v>108.77104704</v>
       </c>
       <c r="P33">
-        <v>255.58913758</v>
+        <v>253.79910976</v>
       </c>
       <c r="Q33">
-        <v>563.5891375799999</v>
+        <v>561.79910976</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1657487640049742</v>
+        <v>0.1671101385234819</v>
       </c>
       <c r="T33">
-        <v>0.8363358665494786</v>
+        <v>0.845827972175405</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.605968017679982</v>
+        <v>5.430781517127482</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4024,22 +4024,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1260220941959677</v>
+        <v>0.1256774412285032</v>
       </c>
       <c r="C34">
-        <v>4169.510768448943</v>
+        <v>4147.14609148446</v>
       </c>
       <c r="D34">
-        <v>5533.854768448943</v>
+        <v>5557.73209148446</v>
       </c>
       <c r="E34">
-        <v>-422.9560000000001</v>
+        <v>-376.7139999999999</v>
       </c>
       <c r="F34">
-        <v>1479.744</v>
+        <v>1525.986</v>
       </c>
       <c r="G34">
         <v>115.4</v>
@@ -4060,28 +4060,28 @@
         <v>444.4</v>
       </c>
       <c r="M34">
-        <v>81.8298432</v>
+        <v>84.3870258</v>
       </c>
       <c r="N34">
-        <v>362.5701567999999</v>
+        <v>360.0129742</v>
       </c>
       <c r="O34">
-        <v>108.77104704</v>
+        <v>108.00389226</v>
       </c>
       <c r="P34">
-        <v>253.79910976</v>
+        <v>252.00908194</v>
       </c>
       <c r="Q34">
-        <v>561.79910976</v>
+        <v>560.00908194</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1671101385234819</v>
+        <v>0.1685121510873182</v>
       </c>
       <c r="T34">
-        <v>0.845827972175405</v>
+        <v>0.8556034242379262</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.430781517127482</v>
+        <v>5.266212380244831</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4106,22 +4106,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1256774412285032</v>
+        <v>0.1253327882610387</v>
       </c>
       <c r="C35">
-        <v>4147.14609148446</v>
+        <v>4124.988357855403</v>
       </c>
       <c r="D35">
-        <v>5557.73209148446</v>
+        <v>5581.816357855403</v>
       </c>
       <c r="E35">
-        <v>-376.7139999999999</v>
+        <v>-330.472</v>
       </c>
       <c r="F35">
-        <v>1525.986</v>
+        <v>1572.228</v>
       </c>
       <c r="G35">
         <v>115.4</v>
@@ -4142,28 +4142,28 @@
         <v>444.4</v>
       </c>
       <c r="M35">
-        <v>84.3870258</v>
+        <v>86.94420840000001</v>
       </c>
       <c r="N35">
-        <v>360.0129742</v>
+        <v>357.4557916</v>
       </c>
       <c r="O35">
-        <v>108.00389226</v>
+        <v>107.23673748</v>
       </c>
       <c r="P35">
-        <v>252.00908194</v>
+        <v>250.21905412</v>
       </c>
       <c r="Q35">
-        <v>560.00908194</v>
+        <v>558.21905412</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1685121510873182</v>
+        <v>0.1699566488803617</v>
       </c>
       <c r="T35">
-        <v>0.8556034242379262</v>
+        <v>0.8656751021205238</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.266212380244831</v>
+        <v>5.111323780825866</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4188,22 +4188,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1253327882610387</v>
+        <v>0.1249881352935742</v>
       </c>
       <c r="C36">
-        <v>4124.988357855403</v>
+        <v>4103.040269619389</v>
       </c>
       <c r="D36">
-        <v>5581.816357855403</v>
+        <v>5606.110269619389</v>
       </c>
       <c r="E36">
-        <v>-330.472</v>
+        <v>-284.23</v>
       </c>
       <c r="F36">
-        <v>1572.228</v>
+        <v>1618.47</v>
       </c>
       <c r="G36">
         <v>115.4</v>
@@ -4224,28 +4224,28 @@
         <v>444.4</v>
       </c>
       <c r="M36">
-        <v>86.94420840000001</v>
+        <v>89.501391</v>
       </c>
       <c r="N36">
-        <v>357.4557916</v>
+        <v>354.898609</v>
       </c>
       <c r="O36">
-        <v>107.23673748</v>
+        <v>106.4695827</v>
       </c>
       <c r="P36">
-        <v>250.21905412</v>
+        <v>248.4290263</v>
       </c>
       <c r="Q36">
-        <v>558.21905412</v>
+        <v>556.4290263</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1699566488803617</v>
+        <v>0.171445592759345</v>
       </c>
       <c r="T36">
-        <v>0.8656751021205238</v>
+        <v>0.8760566777841243</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.111323780825866</v>
+        <v>4.965285958516555</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4270,22 +4270,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1249881352935742</v>
+        <v>0.1246434823261097</v>
       </c>
       <c r="C37">
-        <v>4103.040269619389</v>
+        <v>4081.30457608066</v>
       </c>
       <c r="D37">
-        <v>5606.110269619389</v>
+        <v>5630.616576080661</v>
       </c>
       <c r="E37">
-        <v>-284.23</v>
+        <v>-237.9879999999998</v>
       </c>
       <c r="F37">
-        <v>1618.47</v>
+        <v>1664.712</v>
       </c>
       <c r="G37">
         <v>115.4</v>
@@ -4306,28 +4306,28 @@
         <v>444.4</v>
       </c>
       <c r="M37">
-        <v>89.501391</v>
+        <v>92.05857360000002</v>
       </c>
       <c r="N37">
-        <v>354.898609</v>
+        <v>352.3414263999999</v>
       </c>
       <c r="O37">
-        <v>106.4695827</v>
+        <v>105.70242792</v>
       </c>
       <c r="P37">
-        <v>248.4290263</v>
+        <v>246.6389984799999</v>
       </c>
       <c r="Q37">
-        <v>556.4290263</v>
+        <v>554.6389984799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.171445592759345</v>
+        <v>0.1729810661345465</v>
       </c>
       <c r="T37">
-        <v>0.8760566777841243</v>
+        <v>0.8867626776872125</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.965285958516555</v>
+        <v>4.82736134855776</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4352,22 +4352,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1246434823261098</v>
+        <v>0.1242988293586453</v>
       </c>
       <c r="C38">
-        <v>4081.30457608066</v>
+        <v>4059.784074827281</v>
       </c>
       <c r="D38">
-        <v>5630.61657608066</v>
+        <v>5655.338074827281</v>
       </c>
       <c r="E38">
-        <v>-237.9880000000003</v>
+        <v>-191.7460000000001</v>
       </c>
       <c r="F38">
-        <v>1664.712</v>
+        <v>1710.954</v>
       </c>
       <c r="G38">
         <v>115.4</v>
@@ -4388,28 +4388,28 @@
         <v>444.4</v>
       </c>
       <c r="M38">
-        <v>92.05857359999999</v>
+        <v>94.61575620000001</v>
       </c>
       <c r="N38">
-        <v>352.3414264</v>
+        <v>349.7842438</v>
       </c>
       <c r="O38">
-        <v>105.70242792</v>
+        <v>104.93527314</v>
       </c>
       <c r="P38">
-        <v>246.63899848</v>
+        <v>244.84897066</v>
       </c>
       <c r="Q38">
-        <v>554.6389984800001</v>
+        <v>552.84897066</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1729810661345465</v>
+        <v>0.1745652846962623</v>
       </c>
       <c r="T38">
-        <v>0.8867626776872125</v>
+        <v>0.8978085506030969</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.827361348557762</v>
+        <v>4.696892122921065</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4434,22 +4434,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1242988293586453</v>
+        <v>0.1239541763911807</v>
       </c>
       <c r="C39">
-        <v>4059.784074827281</v>
+        <v>4038.481612795776</v>
       </c>
       <c r="D39">
-        <v>5655.338074827281</v>
+        <v>5680.277612795776</v>
       </c>
       <c r="E39">
-        <v>-191.7460000000001</v>
+        <v>-145.5040000000001</v>
       </c>
       <c r="F39">
-        <v>1710.954</v>
+        <v>1757.196</v>
       </c>
       <c r="G39">
         <v>115.4</v>
@@ -4470,28 +4470,28 @@
         <v>444.4</v>
       </c>
       <c r="M39">
-        <v>94.61575620000001</v>
+        <v>97.1729388</v>
       </c>
       <c r="N39">
-        <v>349.7842438</v>
+        <v>347.2270612</v>
       </c>
       <c r="O39">
-        <v>104.93527314</v>
+        <v>104.16811836</v>
       </c>
       <c r="P39">
-        <v>244.84897066</v>
+        <v>243.05894284</v>
       </c>
       <c r="Q39">
-        <v>552.84897066</v>
+        <v>551.05894284</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1745652846962623</v>
+        <v>0.1762006070825496</v>
       </c>
       <c r="T39">
-        <v>0.8978085506030969</v>
+        <v>0.9092107420001391</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.696892122921065</v>
+        <v>4.573289698633669</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4516,22 +4516,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1239541763911807</v>
+        <v>0.1242920234237162</v>
       </c>
       <c r="C40">
-        <v>4038.481612795776</v>
+        <v>3967.790441379956</v>
       </c>
       <c r="D40">
-        <v>5680.277612795776</v>
+        <v>5655.828441379957</v>
       </c>
       <c r="E40">
-        <v>-145.5040000000001</v>
+        <v>-99.26199999999994</v>
       </c>
       <c r="F40">
-        <v>1757.196</v>
+        <v>1803.438</v>
       </c>
       <c r="G40">
         <v>115.4</v>
@@ -4552,45 +4552,45 @@
         <v>444.4</v>
       </c>
       <c r="M40">
-        <v>97.1729388</v>
+        <v>104.2387164</v>
       </c>
       <c r="N40">
-        <v>347.2270612</v>
+        <v>340.1612835999999</v>
       </c>
       <c r="O40">
-        <v>104.16811836</v>
+        <v>102.04838508</v>
       </c>
       <c r="P40">
-        <v>243.05894284</v>
+        <v>238.11289852</v>
       </c>
       <c r="Q40">
-        <v>551.05894284</v>
+        <v>546.1128985199999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1762006070825496</v>
+        <v>0.1778895465962561</v>
       </c>
       <c r="T40">
-        <v>0.9092107420001391</v>
+        <v>0.9209867757380679</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.573289698633669</v>
+        <v>4.263291177672252</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4598,22 +4598,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1242920234237162</v>
+        <v>0.1239648704562518</v>
       </c>
       <c r="C41">
-        <v>3967.790441379956</v>
+        <v>3945.220470096528</v>
       </c>
       <c r="D41">
-        <v>5655.828441379957</v>
+        <v>5679.500470096528</v>
       </c>
       <c r="E41">
-        <v>-99.26199999999994</v>
+        <v>-53.01999999999998</v>
       </c>
       <c r="F41">
-        <v>1803.438</v>
+        <v>1849.68</v>
       </c>
       <c r="G41">
         <v>115.4</v>
@@ -4634,28 +4634,28 @@
         <v>444.4</v>
       </c>
       <c r="M41">
-        <v>104.2387164</v>
+        <v>106.911504</v>
       </c>
       <c r="N41">
-        <v>340.1612835999999</v>
+        <v>337.4884959999999</v>
       </c>
       <c r="O41">
-        <v>102.04838508</v>
+        <v>101.2465488</v>
       </c>
       <c r="P41">
-        <v>238.11289852</v>
+        <v>236.2419472</v>
       </c>
       <c r="Q41">
-        <v>546.1128985199999</v>
+        <v>544.2419471999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1778895465962561</v>
+        <v>0.1796347840937529</v>
       </c>
       <c r="T41">
-        <v>0.9209867757380679</v>
+        <v>0.9331553439339276</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.263291177672252</v>
+        <v>4.156708898230447</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4680,22 +4680,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1239648704562518</v>
+        <v>0.1236377174887873</v>
       </c>
       <c r="C42">
-        <v>3945.220470096528</v>
+        <v>3922.849486519584</v>
       </c>
       <c r="D42">
-        <v>5679.500470096528</v>
+        <v>5703.371486519584</v>
       </c>
       <c r="E42">
-        <v>-53.01999999999998</v>
+        <v>-6.77800000000002</v>
       </c>
       <c r="F42">
-        <v>1849.68</v>
+        <v>1895.922</v>
       </c>
       <c r="G42">
         <v>115.4</v>
@@ -4716,28 +4716,28 @@
         <v>444.4</v>
       </c>
       <c r="M42">
-        <v>106.911504</v>
+        <v>109.5842916</v>
       </c>
       <c r="N42">
-        <v>337.4884959999999</v>
+        <v>334.8157083999999</v>
       </c>
       <c r="O42">
-        <v>101.2465488</v>
+        <v>100.44471252</v>
       </c>
       <c r="P42">
-        <v>236.2419472</v>
+        <v>234.37099588</v>
       </c>
       <c r="Q42">
-        <v>544.2419471999999</v>
+        <v>542.37099588</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1796347840937529</v>
+        <v>0.1814391821843852</v>
       </c>
       <c r="T42">
-        <v>0.9331553439339276</v>
+        <v>0.9457364059669351</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.156708898230447</v>
+        <v>4.055325754371166</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1236377174887873</v>
+        <v>0.1243395645213228</v>
       </c>
       <c r="C43">
-        <v>3922.849486519584</v>
+        <v>3825.640889268149</v>
       </c>
       <c r="D43">
-        <v>5703.371486519584</v>
+        <v>5652.404889268149</v>
       </c>
       <c r="E43">
-        <v>-6.77800000000002</v>
+        <v>39.46400000000017</v>
       </c>
       <c r="F43">
-        <v>1895.922</v>
+        <v>1942.164</v>
       </c>
       <c r="G43">
         <v>115.4</v>
@@ -4798,45 +4798,45 @@
         <v>444.4</v>
       </c>
       <c r="M43">
-        <v>109.5842916</v>
+        <v>119.0546532</v>
       </c>
       <c r="N43">
-        <v>334.8157083999999</v>
+        <v>325.3453468</v>
       </c>
       <c r="O43">
-        <v>100.44471252</v>
+        <v>97.60360403999998</v>
       </c>
       <c r="P43">
-        <v>234.37099588</v>
+        <v>227.74174276</v>
       </c>
       <c r="Q43">
-        <v>542.37099588</v>
+        <v>535.74174276</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1814391821843852</v>
+        <v>0.1833058008988324</v>
       </c>
       <c r="T43">
-        <v>0.9457364059669351</v>
+        <v>0.9587512977252187</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.055325754371166</v>
+        <v>3.732739444072396</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4844,22 +4844,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1243395645213228</v>
+        <v>0.1240369115538583</v>
       </c>
       <c r="C44">
-        <v>3825.640889268149</v>
+        <v>3801.264746177266</v>
       </c>
       <c r="D44">
-        <v>5652.404889268149</v>
+        <v>5674.270746177266</v>
       </c>
       <c r="E44">
-        <v>39.46399999999971</v>
+        <v>85.7059999999999</v>
       </c>
       <c r="F44">
-        <v>1942.164</v>
+        <v>1988.406</v>
       </c>
       <c r="G44">
         <v>115.4</v>
@@ -4880,28 +4880,28 @@
         <v>444.4</v>
       </c>
       <c r="M44">
-        <v>119.0546532</v>
+        <v>121.8892878</v>
       </c>
       <c r="N44">
-        <v>325.3453468</v>
+        <v>322.5107122</v>
       </c>
       <c r="O44">
-        <v>97.60360404000001</v>
+        <v>96.75321366</v>
       </c>
       <c r="P44">
-        <v>227.74174276</v>
+        <v>225.75749854</v>
       </c>
       <c r="Q44">
-        <v>535.7417427600001</v>
+        <v>533.75749854</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1833058008988323</v>
+        <v>0.1852379150067689</v>
       </c>
       <c r="T44">
-        <v>0.9587512977252186</v>
+        <v>0.972222852352214</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.732739444072397</v>
+        <v>3.645931550024202</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4926,22 +4926,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1240369115538583</v>
+        <v>0.1237342585863938</v>
       </c>
       <c r="C45">
-        <v>3801.264746177266</v>
+        <v>3777.058432545202</v>
       </c>
       <c r="D45">
-        <v>5674.270746177266</v>
+        <v>5696.306432545202</v>
       </c>
       <c r="E45">
-        <v>85.7059999999999</v>
+        <v>131.9479999999999</v>
       </c>
       <c r="F45">
-        <v>1988.406</v>
+        <v>2034.648</v>
       </c>
       <c r="G45">
         <v>115.4</v>
@@ -4962,28 +4962,28 @@
         <v>444.4</v>
       </c>
       <c r="M45">
-        <v>121.8892878</v>
+        <v>124.7239224</v>
       </c>
       <c r="N45">
-        <v>322.5107122</v>
+        <v>319.6760776</v>
       </c>
       <c r="O45">
-        <v>96.75321366</v>
+        <v>95.90282327999999</v>
       </c>
       <c r="P45">
-        <v>225.75749854</v>
+        <v>223.77325432</v>
       </c>
       <c r="Q45">
-        <v>533.75749854</v>
+        <v>531.77325432</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1852379150067689</v>
+        <v>0.1872390331899889</v>
       </c>
       <c r="T45">
-        <v>0.972222852352214</v>
+        <v>0.9861755339301734</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.645931550024202</v>
+        <v>3.563069469341833</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5008,22 +5008,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1237342585863938</v>
+        <v>0.1243136056189293</v>
       </c>
       <c r="C46">
-        <v>3777.058432545202</v>
+        <v>3688.783740222734</v>
       </c>
       <c r="D46">
-        <v>5696.306432545202</v>
+        <v>5654.273740222734</v>
       </c>
       <c r="E46">
-        <v>131.9479999999999</v>
+        <v>178.1899999999998</v>
       </c>
       <c r="F46">
-        <v>2034.648</v>
+        <v>2080.89</v>
       </c>
       <c r="G46">
         <v>115.4</v>
@@ -5044,45 +5044,45 @@
         <v>444.4</v>
       </c>
       <c r="M46">
-        <v>124.7239224</v>
+        <v>133.385049</v>
       </c>
       <c r="N46">
-        <v>319.6760776</v>
+        <v>311.014951</v>
       </c>
       <c r="O46">
-        <v>95.90282327999999</v>
+        <v>93.3044853</v>
       </c>
       <c r="P46">
-        <v>223.77325432</v>
+        <v>217.7104657</v>
       </c>
       <c r="Q46">
-        <v>531.77325432</v>
+        <v>525.7104657</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1872390331899889</v>
+        <v>0.1893129193071442</v>
       </c>
       <c r="T46">
-        <v>0.9861755339301734</v>
+        <v>1.000635585747331</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.563069469341833</v>
+        <v>3.331707738848602</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5090,22 +5090,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1243136056189293</v>
+        <v>0.1240305526514648</v>
       </c>
       <c r="C47">
-        <v>3688.783740222734</v>
+        <v>3662.999974336931</v>
       </c>
       <c r="D47">
-        <v>5654.273740222734</v>
+        <v>5674.731974336932</v>
       </c>
       <c r="E47">
-        <v>178.1899999999998</v>
+        <v>224.432</v>
       </c>
       <c r="F47">
-        <v>2080.89</v>
+        <v>2127.132</v>
       </c>
       <c r="G47">
         <v>115.4</v>
@@ -5126,28 +5126,28 @@
         <v>444.4</v>
       </c>
       <c r="M47">
-        <v>133.385049</v>
+        <v>136.3491612</v>
       </c>
       <c r="N47">
-        <v>311.014951</v>
+        <v>308.0508388</v>
       </c>
       <c r="O47">
-        <v>93.3044853</v>
+        <v>92.41525163999998</v>
       </c>
       <c r="P47">
-        <v>217.7104657</v>
+        <v>215.63558716</v>
       </c>
       <c r="Q47">
-        <v>525.7104657</v>
+        <v>523.63558716</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1893129193071442</v>
+        <v>0.1914636160212311</v>
       </c>
       <c r="T47">
-        <v>1.000635585747331</v>
+        <v>1.015631195039199</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.331707738848602</v>
+        <v>3.259279309743197</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5172,22 +5172,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1240305526514648</v>
+        <v>0.1237474996840003</v>
       </c>
       <c r="C48">
-        <v>3662.999974336931</v>
+        <v>3637.364789583263</v>
       </c>
       <c r="D48">
-        <v>5674.731974336932</v>
+        <v>5695.338789583264</v>
       </c>
       <c r="E48">
-        <v>224.432</v>
+        <v>270.6740000000002</v>
       </c>
       <c r="F48">
-        <v>2127.132</v>
+        <v>2173.374</v>
       </c>
       <c r="G48">
         <v>115.4</v>
@@ -5208,28 +5208,28 @@
         <v>444.4</v>
       </c>
       <c r="M48">
-        <v>136.3491612</v>
+        <v>139.3132734</v>
       </c>
       <c r="N48">
-        <v>308.0508388</v>
+        <v>305.0867266</v>
       </c>
       <c r="O48">
-        <v>92.41525163999998</v>
+        <v>91.52601797999999</v>
       </c>
       <c r="P48">
-        <v>215.63558716</v>
+        <v>213.56070862</v>
       </c>
       <c r="Q48">
-        <v>523.63558716</v>
+        <v>521.56070862</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1914636160212311</v>
+        <v>0.1936954711018874</v>
       </c>
       <c r="T48">
-        <v>1.015631195039199</v>
+        <v>1.031192676379816</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.259279309743197</v>
+        <v>3.189932941450789</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5254,22 +5254,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1237474996840003</v>
+        <v>0.1234644467165358</v>
       </c>
       <c r="C49">
-        <v>3637.364789583263</v>
+        <v>3611.879810501612</v>
       </c>
       <c r="D49">
-        <v>5695.338789583264</v>
+        <v>5716.095810501613</v>
       </c>
       <c r="E49">
-        <v>270.6740000000002</v>
+        <v>316.9159999999999</v>
       </c>
       <c r="F49">
-        <v>2173.374</v>
+        <v>2219.616</v>
       </c>
       <c r="G49">
         <v>115.4</v>
@@ -5290,28 +5290,28 @@
         <v>444.4</v>
       </c>
       <c r="M49">
-        <v>139.3132734</v>
+        <v>142.2773856</v>
       </c>
       <c r="N49">
-        <v>305.0867266</v>
+        <v>302.1226144</v>
       </c>
       <c r="O49">
-        <v>91.52601797999999</v>
+        <v>90.63678431999999</v>
       </c>
       <c r="P49">
-        <v>213.56070862</v>
+        <v>211.48583008</v>
       </c>
       <c r="Q49">
-        <v>521.56070862</v>
+        <v>519.4858300799999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1936954711018874</v>
+        <v>0.1960131667625689</v>
       </c>
       <c r="T49">
-        <v>1.031192676379816</v>
+        <v>1.047352676233534</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.189932941450789</v>
+        <v>3.123476005170564</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5336,22 +5336,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1234644467165358</v>
+        <v>0.1231813937490713</v>
       </c>
       <c r="C50">
-        <v>3611.879810501612</v>
+        <v>3586.546685401444</v>
       </c>
       <c r="D50">
-        <v>5716.095810501613</v>
+        <v>5737.004685401444</v>
       </c>
       <c r="E50">
-        <v>316.9159999999999</v>
+        <v>363.1579999999997</v>
       </c>
       <c r="F50">
-        <v>2219.616</v>
+        <v>2265.858</v>
       </c>
       <c r="G50">
         <v>115.4</v>
@@ -5372,28 +5372,28 @@
         <v>444.4</v>
       </c>
       <c r="M50">
-        <v>142.2773856</v>
+        <v>145.2414978</v>
       </c>
       <c r="N50">
-        <v>302.1226144</v>
+        <v>299.1585022</v>
       </c>
       <c r="O50">
-        <v>90.63678431999999</v>
+        <v>89.74755065999999</v>
       </c>
       <c r="P50">
-        <v>211.48583008</v>
+        <v>209.41095154</v>
       </c>
       <c r="Q50">
-        <v>519.4858300799999</v>
+        <v>517.41095154</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1960131667625689</v>
+        <v>0.1984217524491594</v>
       </c>
       <c r="T50">
-        <v>1.047352676233534</v>
+        <v>1.064146401571711</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.123476005170564</v>
+        <v>3.059731596901778</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1231813937490713</v>
+        <v>0.1256283407816068</v>
       </c>
       <c r="C51">
-        <v>3586.546685401444</v>
+        <v>3364.450515652498</v>
       </c>
       <c r="D51">
-        <v>5737.004685401444</v>
+        <v>5561.150515652498</v>
       </c>
       <c r="E51">
-        <v>363.1579999999997</v>
+        <v>409.3999999999999</v>
       </c>
       <c r="F51">
-        <v>2265.858</v>
+        <v>2312.1</v>
       </c>
       <c r="G51">
         <v>115.4</v>
@@ -5454,45 +5454,45 @@
         <v>444.4</v>
       </c>
       <c r="M51">
-        <v>145.2414978</v>
+        <v>166.23999</v>
       </c>
       <c r="N51">
-        <v>299.1585022</v>
+        <v>278.1600099999999</v>
       </c>
       <c r="O51">
-        <v>89.74755065999999</v>
+        <v>83.44800299999999</v>
       </c>
       <c r="P51">
-        <v>209.41095154</v>
+        <v>194.712007</v>
       </c>
       <c r="Q51">
-        <v>517.41095154</v>
+        <v>502.712007</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1984217524491594</v>
+        <v>0.2009266815632136</v>
       </c>
       <c r="T51">
-        <v>1.064146401571711</v>
+        <v>1.081611875923416</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.059731596901778</v>
+        <v>2.673243664174907</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5500,22 +5500,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1256283407816068</v>
+        <v>0.1253998878141423</v>
       </c>
       <c r="C52">
-        <v>3364.450515652498</v>
+        <v>3334.169107717452</v>
       </c>
       <c r="D52">
-        <v>5561.150515652498</v>
+        <v>5577.111107717453</v>
       </c>
       <c r="E52">
-        <v>409.3999999999999</v>
+        <v>455.6420000000001</v>
       </c>
       <c r="F52">
-        <v>2312.1</v>
+        <v>2358.342</v>
       </c>
       <c r="G52">
         <v>115.4</v>
@@ -5536,28 +5536,28 @@
         <v>444.4</v>
       </c>
       <c r="M52">
-        <v>166.23999</v>
+        <v>169.5647898</v>
       </c>
       <c r="N52">
-        <v>278.1600099999999</v>
+        <v>274.8352101999999</v>
       </c>
       <c r="O52">
-        <v>83.44800299999999</v>
+        <v>82.45056305999998</v>
       </c>
       <c r="P52">
-        <v>194.712007</v>
+        <v>192.38464714</v>
       </c>
       <c r="Q52">
-        <v>502.712007</v>
+        <v>500.38464714</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2009266815632136</v>
+        <v>0.2035338526819231</v>
       </c>
       <c r="T52">
-        <v>1.081611875923416</v>
+        <v>1.099790226779272</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.673243664174907</v>
+        <v>2.620827121740105</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5582,22 +5582,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1253998878141423</v>
+        <v>0.1251714348466778</v>
       </c>
       <c r="C53">
-        <v>3334.169107717452</v>
+        <v>3303.979577789316</v>
       </c>
       <c r="D53">
-        <v>5577.111107717453</v>
+        <v>5593.163577789316</v>
       </c>
       <c r="E53">
-        <v>455.6420000000001</v>
+        <v>501.8839999999998</v>
       </c>
       <c r="F53">
-        <v>2358.342</v>
+        <v>2404.584</v>
       </c>
       <c r="G53">
         <v>115.4</v>
@@ -5618,28 +5618,28 @@
         <v>444.4</v>
       </c>
       <c r="M53">
-        <v>169.5647898</v>
+        <v>172.8895896</v>
       </c>
       <c r="N53">
-        <v>274.8352101999999</v>
+        <v>271.5104104</v>
       </c>
       <c r="O53">
-        <v>82.45056305999998</v>
+        <v>81.45312311999999</v>
       </c>
       <c r="P53">
-        <v>192.38464714</v>
+        <v>190.05728728</v>
       </c>
       <c r="Q53">
-        <v>500.38464714</v>
+        <v>498.05728728</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2035338526819231</v>
+        <v>0.2062496559305788</v>
       </c>
       <c r="T53">
-        <v>1.099790226779272</v>
+        <v>1.118726008920788</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.620827121740105</v>
+        <v>2.57042660016818</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5664,22 +5664,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1251714348466778</v>
+        <v>0.1249429818792133</v>
       </c>
       <c r="C54">
-        <v>3303.979577789316</v>
+        <v>3273.882721509203</v>
       </c>
       <c r="D54">
-        <v>5593.163577789316</v>
+        <v>5609.308721509204</v>
       </c>
       <c r="E54">
-        <v>501.8839999999998</v>
+        <v>548.126</v>
       </c>
       <c r="F54">
-        <v>2404.584</v>
+        <v>2450.826</v>
       </c>
       <c r="G54">
         <v>115.4</v>
@@ -5700,28 +5700,28 @@
         <v>444.4</v>
       </c>
       <c r="M54">
-        <v>172.8895896</v>
+        <v>176.2143894</v>
       </c>
       <c r="N54">
-        <v>271.5104104</v>
+        <v>268.1856106</v>
       </c>
       <c r="O54">
-        <v>81.45312311999999</v>
+        <v>80.45568317999998</v>
       </c>
       <c r="P54">
-        <v>190.05728728</v>
+        <v>187.72992742</v>
       </c>
       <c r="Q54">
-        <v>498.05728728</v>
+        <v>495.72992742</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2062496559305788</v>
+        <v>0.2090810252749219</v>
       </c>
       <c r="T54">
-        <v>1.118726008920788</v>
+        <v>1.138467569025773</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.57042660016818</v>
+        <v>2.521927985070668</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5746,22 +5746,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1249429818792133</v>
+        <v>0.1261887289117488</v>
       </c>
       <c r="C55">
-        <v>3273.882721509203</v>
+        <v>3140.715852948751</v>
       </c>
       <c r="D55">
-        <v>5609.308721509204</v>
+        <v>5522.383852948751</v>
       </c>
       <c r="E55">
-        <v>548.126</v>
+        <v>594.3680000000002</v>
       </c>
       <c r="F55">
-        <v>2450.826</v>
+        <v>2497.068</v>
       </c>
       <c r="G55">
         <v>115.4</v>
@@ -5782,45 +5782,45 @@
         <v>444.4</v>
       </c>
       <c r="M55">
-        <v>176.2143894</v>
+        <v>189.2777544</v>
       </c>
       <c r="N55">
-        <v>268.1856106</v>
+        <v>255.1222456</v>
       </c>
       <c r="O55">
-        <v>80.45568317999998</v>
+        <v>76.53667367999998</v>
       </c>
       <c r="P55">
-        <v>187.72992742</v>
+        <v>178.58557192</v>
       </c>
       <c r="Q55">
-        <v>495.72992742</v>
+        <v>486.58557192</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2090810252749219</v>
+        <v>0.2120354976342366</v>
       </c>
       <c r="T55">
-        <v>1.138467569025773</v>
+        <v>1.159067457830975</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.521927985070668</v>
+        <v>2.347872318163977</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5828,22 +5828,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1261887289117488</v>
+        <v>0.1259875759442843</v>
       </c>
       <c r="C56">
-        <v>3140.715852948751</v>
+        <v>3108.326920414843</v>
       </c>
       <c r="D56">
-        <v>5522.383852948751</v>
+        <v>5536.236920414844</v>
       </c>
       <c r="E56">
-        <v>594.3680000000002</v>
+        <v>640.6099999999999</v>
       </c>
       <c r="F56">
-        <v>2497.068</v>
+        <v>2543.31</v>
       </c>
       <c r="G56">
         <v>115.4</v>
@@ -5864,28 +5864,28 @@
         <v>444.4</v>
       </c>
       <c r="M56">
-        <v>189.2777544</v>
+        <v>192.782898</v>
       </c>
       <c r="N56">
-        <v>255.1222456</v>
+        <v>251.617102</v>
       </c>
       <c r="O56">
-        <v>76.53667367999998</v>
+        <v>75.48513059999999</v>
       </c>
       <c r="P56">
-        <v>178.58557192</v>
+        <v>176.1319714</v>
       </c>
       <c r="Q56">
-        <v>486.58557192</v>
+        <v>484.1319714</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2120354976342366</v>
+        <v>0.2151212798761874</v>
       </c>
       <c r="T56">
-        <v>1.159067457830975</v>
+        <v>1.180582897249742</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.347872318163977</v>
+        <v>2.305183730560996</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5910,22 +5910,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1259875759442843</v>
+        <v>0.1257864229768198</v>
       </c>
       <c r="C57">
-        <v>3108.326920414843</v>
+        <v>3076.007664346657</v>
       </c>
       <c r="D57">
-        <v>5536.236920414844</v>
+        <v>5550.159664346657</v>
       </c>
       <c r="E57">
-        <v>640.6099999999999</v>
+        <v>686.8520000000001</v>
       </c>
       <c r="F57">
-        <v>2543.31</v>
+        <v>2589.552</v>
       </c>
       <c r="G57">
         <v>115.4</v>
@@ -5946,28 +5946,28 @@
         <v>444.4</v>
       </c>
       <c r="M57">
-        <v>192.782898</v>
+        <v>196.2880416</v>
       </c>
       <c r="N57">
-        <v>251.617102</v>
+        <v>248.1119584</v>
       </c>
       <c r="O57">
-        <v>75.48513059999999</v>
+        <v>74.43358751999999</v>
       </c>
       <c r="P57">
-        <v>176.1319714</v>
+        <v>173.67837088</v>
       </c>
       <c r="Q57">
-        <v>484.1319714</v>
+        <v>481.67837088</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2151212798761874</v>
+        <v>0.2183473249473178</v>
       </c>
       <c r="T57">
-        <v>1.180582897249742</v>
+        <v>1.203076311187543</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.305183730560996</v>
+        <v>2.264019735372407</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5992,22 +5992,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1257864229768198</v>
+        <v>0.1255852700093553</v>
       </c>
       <c r="C58">
-        <v>3076.007664346657</v>
+        <v>3043.758611744769</v>
       </c>
       <c r="D58">
-        <v>5550.159664346657</v>
+        <v>5564.152611744769</v>
       </c>
       <c r="E58">
-        <v>686.8520000000001</v>
+        <v>733.0940000000003</v>
       </c>
       <c r="F58">
-        <v>2589.552</v>
+        <v>2635.794</v>
       </c>
       <c r="G58">
         <v>115.4</v>
@@ -6028,28 +6028,28 @@
         <v>444.4</v>
       </c>
       <c r="M58">
-        <v>196.2880416</v>
+        <v>199.7931852</v>
       </c>
       <c r="N58">
-        <v>248.1119584</v>
+        <v>244.6068147999999</v>
       </c>
       <c r="O58">
-        <v>74.43358751999999</v>
+        <v>73.38204443999997</v>
       </c>
       <c r="P58">
-        <v>173.67837088</v>
+        <v>171.22477036</v>
       </c>
       <c r="Q58">
-        <v>481.67837088</v>
+        <v>479.22477036</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2183473249473178</v>
+        <v>0.2217234186264078</v>
       </c>
       <c r="T58">
-        <v>1.203076311187543</v>
+        <v>1.226615930424777</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.264019735372407</v>
+        <v>2.224300090892188</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6074,22 +6074,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1255852700093553</v>
+        <v>0.1253841170418908</v>
       </c>
       <c r="C59">
-        <v>3043.758611744769</v>
+        <v>3011.580294937844</v>
       </c>
       <c r="D59">
-        <v>5564.152611744769</v>
+        <v>5578.216294937844</v>
       </c>
       <c r="E59">
-        <v>733.0940000000003</v>
+        <v>779.336</v>
       </c>
       <c r="F59">
-        <v>2635.794</v>
+        <v>2682.036</v>
       </c>
       <c r="G59">
         <v>115.4</v>
@@ -6110,28 +6110,28 @@
         <v>444.4</v>
       </c>
       <c r="M59">
-        <v>199.7931852</v>
+        <v>203.2983288</v>
       </c>
       <c r="N59">
-        <v>244.6068147999999</v>
+        <v>241.1016712</v>
       </c>
       <c r="O59">
-        <v>73.38204443999997</v>
+        <v>72.33050135999999</v>
       </c>
       <c r="P59">
-        <v>171.22477036</v>
+        <v>168.77116984</v>
       </c>
       <c r="Q59">
-        <v>479.22477036</v>
+        <v>476.77116984</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2217234186264078</v>
+        <v>0.2252602786711687</v>
       </c>
       <c r="T59">
-        <v>1.226615930424777</v>
+        <v>1.251276483911403</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.224300090892188</v>
+        <v>2.185950089325083</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6156,22 +6156,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1253841170418908</v>
+        <v>0.1251829640744264</v>
       </c>
       <c r="C60">
-        <v>3011.580294937844</v>
+        <v>2979.473251650137</v>
       </c>
       <c r="D60">
-        <v>5578.216294937844</v>
+        <v>5592.351251650137</v>
       </c>
       <c r="E60">
-        <v>779.3359999999996</v>
+        <v>825.5779999999997</v>
       </c>
       <c r="F60">
-        <v>2682.036</v>
+        <v>2728.278</v>
       </c>
       <c r="G60">
         <v>115.4</v>
@@ -6192,28 +6192,28 @@
         <v>444.4</v>
       </c>
       <c r="M60">
-        <v>203.2983288</v>
+        <v>206.8034724</v>
       </c>
       <c r="N60">
-        <v>241.1016712</v>
+        <v>237.5965276</v>
       </c>
       <c r="O60">
-        <v>72.33050136</v>
+        <v>71.27895827999998</v>
       </c>
       <c r="P60">
-        <v>168.77116984</v>
+        <v>166.31756932</v>
       </c>
       <c r="Q60">
-        <v>476.77116984</v>
+        <v>474.31756932</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2252602786711687</v>
+        <v>0.2289696684742106</v>
       </c>
       <c r="T60">
-        <v>1.251276483911403</v>
+        <v>1.277139991226645</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.185950089325083</v>
+        <v>2.148900087811098</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6238,22 +6238,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1251829640744264</v>
+        <v>0.1249818111069619</v>
       </c>
       <c r="C61">
-        <v>2979.473251650137</v>
+        <v>2947.438025070027</v>
       </c>
       <c r="D61">
-        <v>5592.351251650137</v>
+        <v>5606.558025070028</v>
       </c>
       <c r="E61">
-        <v>825.5779999999997</v>
+        <v>871.8199999999999</v>
       </c>
       <c r="F61">
-        <v>2728.278</v>
+        <v>2774.52</v>
       </c>
       <c r="G61">
         <v>115.4</v>
@@ -6274,28 +6274,28 @@
         <v>444.4</v>
       </c>
       <c r="M61">
-        <v>206.8034724</v>
+        <v>210.308616</v>
       </c>
       <c r="N61">
-        <v>237.5965276</v>
+        <v>234.0913839999999</v>
       </c>
       <c r="O61">
-        <v>71.27895827999998</v>
+        <v>70.22741519999998</v>
       </c>
       <c r="P61">
-        <v>166.31756932</v>
+        <v>163.8639688</v>
       </c>
       <c r="Q61">
-        <v>474.31756932</v>
+        <v>471.8639688</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2289696684742106</v>
+        <v>0.2328645277674047</v>
       </c>
       <c r="T61">
-        <v>1.277139991226645</v>
+        <v>1.304296673907649</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.148900087811098</v>
+        <v>2.11308508634758</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6320,22 +6320,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1249818111069619</v>
+        <v>0.1247806581394974</v>
       </c>
       <c r="C62">
-        <v>2947.438025070027</v>
+        <v>2915.475163919603</v>
       </c>
       <c r="D62">
-        <v>5606.558025070028</v>
+        <v>5620.837163919603</v>
       </c>
       <c r="E62">
-        <v>871.8199999999999</v>
+        <v>918.0619999999997</v>
       </c>
       <c r="F62">
-        <v>2774.52</v>
+        <v>2820.762</v>
       </c>
       <c r="G62">
         <v>115.4</v>
@@ -6356,28 +6356,28 @@
         <v>444.4</v>
       </c>
       <c r="M62">
-        <v>210.308616</v>
+        <v>213.8137596</v>
       </c>
       <c r="N62">
-        <v>234.0913839999999</v>
+        <v>230.5862404</v>
       </c>
       <c r="O62">
-        <v>70.22741519999998</v>
+        <v>69.17587211999999</v>
       </c>
       <c r="P62">
-        <v>163.8639688</v>
+        <v>161.41036828</v>
       </c>
       <c r="Q62">
-        <v>471.8639688</v>
+        <v>469.41036828</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2328645277674047</v>
+        <v>0.2369591234346086</v>
       </c>
       <c r="T62">
-        <v>1.304296673907649</v>
+        <v>1.33284600698255</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.11308508634758</v>
+        <v>2.078444347227128</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6402,22 +6402,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1247806581394974</v>
+        <v>0.1245795051720329</v>
       </c>
       <c r="C63">
-        <v>2915.475163919603</v>
+        <v>2883.585222525303</v>
       </c>
       <c r="D63">
-        <v>5620.837163919603</v>
+        <v>5635.189222525303</v>
       </c>
       <c r="E63">
-        <v>918.0619999999997</v>
+        <v>964.3039999999999</v>
       </c>
       <c r="F63">
-        <v>2820.762</v>
+        <v>2867.004</v>
       </c>
       <c r="G63">
         <v>115.4</v>
@@ -6438,28 +6438,28 @@
         <v>444.4</v>
       </c>
       <c r="M63">
-        <v>213.8137596</v>
+        <v>217.3189032</v>
       </c>
       <c r="N63">
-        <v>230.5862404</v>
+        <v>227.0810968</v>
       </c>
       <c r="O63">
-        <v>69.17587211999999</v>
+        <v>68.12432903999998</v>
       </c>
       <c r="P63">
-        <v>161.41036828</v>
+        <v>158.95676776</v>
       </c>
       <c r="Q63">
-        <v>469.41036828</v>
+        <v>466.95676776</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2369591234346086</v>
+        <v>0.2412692241369286</v>
       </c>
       <c r="T63">
-        <v>1.33284600698255</v>
+        <v>1.362897936535078</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.078444347227128</v>
+        <v>2.044921051304109</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6484,22 +6484,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1245795051720329</v>
+        <v>0.1243783522045684</v>
       </c>
       <c r="C64">
-        <v>2883.585222525303</v>
+        <v>2851.768760889659</v>
       </c>
       <c r="D64">
-        <v>5635.189222525303</v>
+        <v>5649.61476088966</v>
       </c>
       <c r="E64">
-        <v>964.3039999999999</v>
+        <v>1010.546</v>
       </c>
       <c r="F64">
-        <v>2867.004</v>
+        <v>2913.246</v>
       </c>
       <c r="G64">
         <v>115.4</v>
@@ -6520,28 +6520,28 @@
         <v>444.4</v>
       </c>
       <c r="M64">
-        <v>217.3189032</v>
+        <v>220.8240468</v>
       </c>
       <c r="N64">
-        <v>227.0810968</v>
+        <v>223.5759532</v>
       </c>
       <c r="O64">
-        <v>68.12432903999998</v>
+        <v>67.07278595999999</v>
       </c>
       <c r="P64">
-        <v>158.95676776</v>
+        <v>156.50316724</v>
       </c>
       <c r="Q64">
-        <v>466.95676776</v>
+        <v>464.50316724</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2412692241369286</v>
+        <v>0.2458123032555903</v>
       </c>
       <c r="T64">
-        <v>1.362897936535078</v>
+        <v>1.394574294712068</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.044921051304109</v>
+        <v>2.012461986997695</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6566,22 +6566,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1243783522045684</v>
+        <v>0.1305387992371039</v>
       </c>
       <c r="C65">
-        <v>2851.768760889659</v>
+        <v>2394.804012844724</v>
       </c>
       <c r="D65">
-        <v>5649.61476088966</v>
+        <v>5238.892012844724</v>
       </c>
       <c r="E65">
-        <v>1010.546</v>
+        <v>1056.788</v>
       </c>
       <c r="F65">
-        <v>2913.246</v>
+        <v>2959.488</v>
       </c>
       <c r="G65">
         <v>115.4</v>
@@ -6602,45 +6602,45 @@
         <v>444.4</v>
       </c>
       <c r="M65">
-        <v>220.8240468</v>
+        <v>266.35392</v>
       </c>
       <c r="N65">
-        <v>223.5759532</v>
+        <v>178.04608</v>
       </c>
       <c r="O65">
-        <v>67.07278595999999</v>
+        <v>53.41382400000001</v>
       </c>
       <c r="P65">
-        <v>156.50316724</v>
+        <v>124.632256</v>
       </c>
       <c r="Q65">
-        <v>464.50316724</v>
+        <v>432.632256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2458123032555903</v>
+        <v>0.2506077756586219</v>
       </c>
       <c r="T65">
-        <v>1.394574294712068</v>
+        <v>1.428010450565556</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.012461986997695</v>
+        <v>1.668456766095277</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6648,22 +6648,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1305387992371039</v>
+        <v>0.1304370462696394</v>
       </c>
       <c r="C66">
-        <v>2394.804012844724</v>
+        <v>2354.860351834896</v>
       </c>
       <c r="D66">
-        <v>5238.892012844724</v>
+        <v>5245.190351834896</v>
       </c>
       <c r="E66">
-        <v>1056.788</v>
+        <v>1103.03</v>
       </c>
       <c r="F66">
-        <v>2959.488</v>
+        <v>3005.73</v>
       </c>
       <c r="G66">
         <v>115.4</v>
@@ -6684,28 +6684,28 @@
         <v>444.4</v>
       </c>
       <c r="M66">
-        <v>266.35392</v>
+        <v>270.5157</v>
       </c>
       <c r="N66">
-        <v>178.04608</v>
+        <v>173.8843</v>
       </c>
       <c r="O66">
-        <v>53.41382400000001</v>
+        <v>52.16529</v>
       </c>
       <c r="P66">
-        <v>124.632256</v>
+        <v>121.71901</v>
       </c>
       <c r="Q66">
-        <v>432.632256</v>
+        <v>429.71901</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2506077756586219</v>
+        <v>0.2556772750561125</v>
       </c>
       <c r="T66">
-        <v>1.428010450565556</v>
+        <v>1.463357243896386</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.668456766095277</v>
+        <v>1.642788200463042</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6730,22 +6730,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1304370462696394</v>
+        <v>0.1303352933021749</v>
       </c>
       <c r="C67">
-        <v>2354.860351834896</v>
+        <v>2314.93185312373</v>
       </c>
       <c r="D67">
-        <v>5245.190351834896</v>
+        <v>5251.503853123731</v>
       </c>
       <c r="E67">
-        <v>1103.03</v>
+        <v>1149.272</v>
       </c>
       <c r="F67">
-        <v>3005.73</v>
+        <v>3051.972</v>
       </c>
       <c r="G67">
         <v>115.4</v>
@@ -6766,28 +6766,28 @@
         <v>444.4</v>
       </c>
       <c r="M67">
-        <v>270.5157</v>
+        <v>274.67748</v>
       </c>
       <c r="N67">
-        <v>173.8843</v>
+        <v>169.72252</v>
       </c>
       <c r="O67">
-        <v>52.16529</v>
+        <v>50.91675599999999</v>
       </c>
       <c r="P67">
-        <v>121.71901</v>
+        <v>118.805764</v>
       </c>
       <c r="Q67">
-        <v>429.71901</v>
+        <v>426.805764</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2556772750561125</v>
+        <v>0.2610449803005144</v>
       </c>
       <c r="T67">
-        <v>1.463357243896386</v>
+        <v>1.500783260364325</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.642788200463042</v>
+        <v>1.617897470152995</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6812,22 +6812,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1303352933021749</v>
+        <v>0.1302335403347104</v>
       </c>
       <c r="C68">
-        <v>2314.93185312373</v>
+        <v>2275.018571528622</v>
       </c>
       <c r="D68">
-        <v>5251.503853123731</v>
+        <v>5257.832571528623</v>
       </c>
       <c r="E68">
-        <v>1149.272</v>
+        <v>1195.514</v>
       </c>
       <c r="F68">
-        <v>3051.972</v>
+        <v>3098.214</v>
       </c>
       <c r="G68">
         <v>115.4</v>
@@ -6848,28 +6848,28 @@
         <v>444.4</v>
       </c>
       <c r="M68">
-        <v>274.67748</v>
+        <v>278.83926</v>
       </c>
       <c r="N68">
-        <v>169.72252</v>
+        <v>165.56074</v>
       </c>
       <c r="O68">
-        <v>50.91675599999999</v>
+        <v>49.668222</v>
       </c>
       <c r="P68">
-        <v>118.805764</v>
+        <v>115.892518</v>
       </c>
       <c r="Q68">
-        <v>426.805764</v>
+        <v>423.892518</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2610449803005144</v>
+        <v>0.266738001014274</v>
       </c>
       <c r="T68">
-        <v>1.500783260364325</v>
+        <v>1.540477520254562</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.617897470152995</v>
+        <v>1.593749746717876</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6894,22 +6894,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1302335403347104</v>
+        <v>0.1301317873672459</v>
       </c>
       <c r="C69">
-        <v>2275.018571528622</v>
+        <v>2235.120562131534</v>
       </c>
       <c r="D69">
-        <v>5257.832571528623</v>
+        <v>5264.176562131534</v>
       </c>
       <c r="E69">
-        <v>1195.514</v>
+        <v>1241.756</v>
       </c>
       <c r="F69">
-        <v>3098.214</v>
+        <v>3144.456</v>
       </c>
       <c r="G69">
         <v>115.4</v>
@@ -6930,28 +6930,28 @@
         <v>444.4</v>
       </c>
       <c r="M69">
-        <v>278.83926</v>
+        <v>283.00104</v>
       </c>
       <c r="N69">
-        <v>165.56074</v>
+        <v>161.39896</v>
       </c>
       <c r="O69">
-        <v>49.668222</v>
+        <v>48.41968799999999</v>
       </c>
       <c r="P69">
-        <v>115.892518</v>
+        <v>112.979272</v>
       </c>
       <c r="Q69">
-        <v>423.892518</v>
+        <v>420.979272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.266738001014274</v>
+        <v>0.2727868355226435</v>
       </c>
       <c r="T69">
-        <v>1.540477520254562</v>
+        <v>1.58265267138794</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.593749746717876</v>
+        <v>1.570312250442613</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6976,22 +6976,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1301317873672459</v>
+        <v>0.1300300343997814</v>
       </c>
       <c r="C70">
-        <v>2235.120562131534</v>
+        <v>2195.237880280586</v>
       </c>
       <c r="D70">
-        <v>5264.176562131534</v>
+        <v>5270.535880280587</v>
       </c>
       <c r="E70">
-        <v>1241.756</v>
+        <v>1287.998</v>
       </c>
       <c r="F70">
-        <v>3144.456</v>
+        <v>3190.698</v>
       </c>
       <c r="G70">
         <v>115.4</v>
@@ -7012,28 +7012,28 @@
         <v>444.4</v>
       </c>
       <c r="M70">
-        <v>283.00104</v>
+        <v>287.16282</v>
       </c>
       <c r="N70">
-        <v>161.39896</v>
+        <v>157.23718</v>
       </c>
       <c r="O70">
-        <v>48.41968799999999</v>
+        <v>47.17115399999999</v>
       </c>
       <c r="P70">
-        <v>112.979272</v>
+        <v>110.066026</v>
       </c>
       <c r="Q70">
-        <v>420.979272</v>
+        <v>418.066026</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2727868355226435</v>
+        <v>0.2792259174186498</v>
       </c>
       <c r="T70">
-        <v>1.58265267138794</v>
+        <v>1.627548800013793</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.570312250442613</v>
+        <v>1.547554101885474</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7058,22 +7058,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1300300343997814</v>
+        <v>0.1299282814323169</v>
       </c>
       <c r="C71">
-        <v>2195.237880280586</v>
+        <v>2155.370581591681</v>
       </c>
       <c r="D71">
-        <v>5270.535880280587</v>
+        <v>5276.910581591681</v>
       </c>
       <c r="E71">
-        <v>1287.998</v>
+        <v>1334.24</v>
       </c>
       <c r="F71">
-        <v>3190.698</v>
+        <v>3236.94</v>
       </c>
       <c r="G71">
         <v>115.4</v>
@@ -7094,28 +7094,28 @@
         <v>444.4</v>
       </c>
       <c r="M71">
-        <v>287.16282</v>
+        <v>291.3246</v>
       </c>
       <c r="N71">
-        <v>157.23718</v>
+        <v>153.0754</v>
       </c>
       <c r="O71">
-        <v>47.17115399999999</v>
+        <v>45.92262</v>
       </c>
       <c r="P71">
-        <v>110.066026</v>
+        <v>107.15278</v>
       </c>
       <c r="Q71">
-        <v>418.066026</v>
+        <v>415.15278</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2792259174186498</v>
+        <v>0.2860942714410564</v>
       </c>
       <c r="T71">
-        <v>1.627548800013793</v>
+        <v>1.67543800388137</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.547554101885474</v>
+        <v>1.525446186144253</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7140,22 +7140,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1299282814323169</v>
+        <v>0.1298265284648524</v>
       </c>
       <c r="C72">
-        <v>2155.370581591681</v>
+        <v>2115.518721950106</v>
       </c>
       <c r="D72">
-        <v>5276.910581591681</v>
+        <v>5283.300721950107</v>
       </c>
       <c r="E72">
-        <v>1334.24</v>
+        <v>1380.482</v>
       </c>
       <c r="F72">
-        <v>3236.94</v>
+        <v>3283.182</v>
       </c>
       <c r="G72">
         <v>115.4</v>
@@ -7176,28 +7176,28 @@
         <v>444.4</v>
       </c>
       <c r="M72">
-        <v>291.3246</v>
+        <v>295.48638</v>
       </c>
       <c r="N72">
-        <v>153.0754</v>
+        <v>148.91362</v>
       </c>
       <c r="O72">
-        <v>45.92262</v>
+        <v>44.674086</v>
       </c>
       <c r="P72">
-        <v>107.15278</v>
+        <v>104.239534</v>
       </c>
       <c r="Q72">
-        <v>415.15278</v>
+        <v>412.239534</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2860942714410564</v>
+        <v>0.2934363050512153</v>
       </c>
       <c r="T72">
-        <v>1.67543800388137</v>
+        <v>1.726629911463953</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.525446186144253</v>
+        <v>1.503961028592925</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7222,22 +7222,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1298265284648524</v>
+        <v>0.1630187268972254</v>
       </c>
       <c r="C73">
-        <v>2115.518721950107</v>
+        <v>573.232782702903</v>
       </c>
       <c r="D73">
-        <v>5283.300721950107</v>
+        <v>3787.256782702902</v>
       </c>
       <c r="E73">
-        <v>1380.482</v>
+        <v>1426.723999999999</v>
       </c>
       <c r="F73">
-        <v>3283.182</v>
+        <v>3329.424</v>
       </c>
       <c r="G73">
         <v>115.4</v>
@@ -7258,45 +7258,45 @@
         <v>444.4</v>
       </c>
       <c r="M73">
-        <v>295.48638</v>
+        <v>488.7594432</v>
       </c>
       <c r="N73">
-        <v>148.91362</v>
+        <v>-44.35944319999999</v>
       </c>
       <c r="O73">
-        <v>44.674086</v>
+        <v>-13.30783296</v>
       </c>
       <c r="P73">
-        <v>104.239534</v>
+        <v>-31.05161023999999</v>
       </c>
       <c r="Q73">
-        <v>412.239534</v>
+        <v>276.94838976</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2934363050512152</v>
+        <v>0.307691642197685</v>
       </c>
       <c r="T73">
-        <v>1.726629911463952</v>
+        <v>1.826024430817677</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.3</v>
+        <v>0.2727722233398273</v>
       </c>
       <c r="W73">
-        <v>0.063</v>
+        <v>0.1067570376137134</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.503961028592925</v>
+        <v>0.9092407444660908</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7304,22 +7304,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1630187268972254</v>
+        <v>0.1640287268972254</v>
       </c>
       <c r="C74">
-        <v>573.232782702903</v>
+        <v>494.6371453855086</v>
       </c>
       <c r="D74">
-        <v>3787.256782702902</v>
+        <v>3754.903145385508</v>
       </c>
       <c r="E74">
-        <v>1426.723999999999</v>
+        <v>1472.966</v>
       </c>
       <c r="F74">
-        <v>3329.424</v>
+        <v>3375.666</v>
       </c>
       <c r="G74">
         <v>115.4</v>
@@ -7340,37 +7340,37 @@
         <v>444.4</v>
       </c>
       <c r="M74">
-        <v>488.7594432</v>
+        <v>495.5477688</v>
       </c>
       <c r="N74">
-        <v>-44.35944319999999</v>
+        <v>-51.14776880000005</v>
       </c>
       <c r="O74">
-        <v>-13.30783296</v>
+        <v>-15.34433064000002</v>
       </c>
       <c r="P74">
-        <v>-31.05161023999999</v>
+        <v>-35.80343816000003</v>
       </c>
       <c r="Q74">
-        <v>276.94838976</v>
+        <v>272.19656184</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.307691642197685</v>
+        <v>0.3173913326494511</v>
       </c>
       <c r="T74">
-        <v>1.826024430817677</v>
+        <v>1.893654965292406</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2727722233398273</v>
+        <v>0.2690356175406515</v>
       </c>
       <c r="W74">
-        <v>0.1067570376137134</v>
+        <v>0.1073055713450324</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9092407444660908</v>
+        <v>0.8967853918021716</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7386,22 +7386,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1640287268972254</v>
+        <v>0.1650387268972254</v>
       </c>
       <c r="C75">
-        <v>494.6371453855086</v>
+        <v>416.5896047233032</v>
       </c>
       <c r="D75">
-        <v>3754.903145385508</v>
+        <v>3723.097604723303</v>
       </c>
       <c r="E75">
-        <v>1472.966</v>
+        <v>1519.208</v>
       </c>
       <c r="F75">
-        <v>3375.666</v>
+        <v>3421.908</v>
       </c>
       <c r="G75">
         <v>115.4</v>
@@ -7422,37 +7422,37 @@
         <v>444.4</v>
       </c>
       <c r="M75">
-        <v>495.5477688</v>
+        <v>502.3360944</v>
       </c>
       <c r="N75">
-        <v>-51.14776880000005</v>
+        <v>-57.93609440000006</v>
       </c>
       <c r="O75">
-        <v>-15.34433064000002</v>
+        <v>-17.38082832000002</v>
       </c>
       <c r="P75">
-        <v>-35.80343816000003</v>
+        <v>-40.55526608000004</v>
       </c>
       <c r="Q75">
-        <v>272.19656184</v>
+        <v>267.44473392</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3173913326494511</v>
+        <v>0.3278371531359685</v>
       </c>
       <c r="T75">
-        <v>1.893654965292406</v>
+        <v>1.966487848572883</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2690356175406515</v>
+        <v>0.2654000010873994</v>
       </c>
       <c r="W75">
-        <v>0.1073055713450324</v>
+        <v>0.1078392798403698</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8967853918021716</v>
+        <v>0.8846666702913314</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7468,22 +7468,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1650387268972254</v>
+        <v>0.1660487268972254</v>
       </c>
       <c r="C76">
-        <v>416.5896047233032</v>
+        <v>339.0763499017507</v>
       </c>
       <c r="D76">
-        <v>3723.097604723303</v>
+        <v>3691.82634990175</v>
       </c>
       <c r="E76">
-        <v>1519.208</v>
+        <v>1565.45</v>
       </c>
       <c r="F76">
-        <v>3421.908</v>
+        <v>3468.15</v>
       </c>
       <c r="G76">
         <v>115.4</v>
@@ -7504,37 +7504,37 @@
         <v>444.4</v>
       </c>
       <c r="M76">
-        <v>502.3360944</v>
+        <v>509.12442</v>
       </c>
       <c r="N76">
-        <v>-57.93609440000006</v>
+        <v>-64.72442000000001</v>
       </c>
       <c r="O76">
-        <v>-17.38082832000002</v>
+        <v>-19.417326</v>
       </c>
       <c r="P76">
-        <v>-40.55526608000004</v>
+        <v>-45.30709400000001</v>
       </c>
       <c r="Q76">
-        <v>267.44473392</v>
+        <v>262.692906</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3278371531359685</v>
+        <v>0.3391186392614072</v>
       </c>
       <c r="T76">
-        <v>1.966487848572883</v>
+        <v>2.045147362515798</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2654000010873994</v>
+        <v>0.2618613344062342</v>
       </c>
       <c r="W76">
-        <v>0.1078392798403698</v>
+        <v>0.1083587561091648</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8846666702913314</v>
+        <v>0.872871114687447</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7550,22 +7550,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1660487268972254</v>
+        <v>0.1670587268972254</v>
       </c>
       <c r="C77">
-        <v>339.0763499017507</v>
+        <v>262.084030243841</v>
       </c>
       <c r="D77">
-        <v>3691.82634990175</v>
+        <v>3661.076030243841</v>
       </c>
       <c r="E77">
-        <v>1565.45</v>
+        <v>1611.692</v>
       </c>
       <c r="F77">
-        <v>3468.15</v>
+        <v>3514.392</v>
       </c>
       <c r="G77">
         <v>115.4</v>
@@ -7586,37 +7586,37 @@
         <v>444.4</v>
       </c>
       <c r="M77">
-        <v>509.12442</v>
+        <v>515.9127456</v>
       </c>
       <c r="N77">
-        <v>-64.72442000000001</v>
+        <v>-71.51274560000002</v>
       </c>
       <c r="O77">
-        <v>-19.417326</v>
+        <v>-21.45382368</v>
       </c>
       <c r="P77">
-        <v>-45.30709400000001</v>
+        <v>-50.05892192000002</v>
       </c>
       <c r="Q77">
-        <v>262.692906</v>
+        <v>257.94107808</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3391186392614072</v>
+        <v>0.3513402492306325</v>
       </c>
       <c r="T77">
-        <v>2.045147362515798</v>
+        <v>2.130361835953956</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2618613344062342</v>
+        <v>0.2584157905324679</v>
       </c>
       <c r="W77">
-        <v>0.1083587561091648</v>
+        <v>0.1088645619498337</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.872871114687447</v>
+        <v>0.8613859684415597</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7632,22 +7632,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1670587268972254</v>
+        <v>0.1680687268972254</v>
       </c>
       <c r="C78">
-        <v>262.084030243841</v>
+        <v>185.5997362052804</v>
       </c>
       <c r="D78">
-        <v>3661.076030243841</v>
+        <v>3630.83373620528</v>
       </c>
       <c r="E78">
-        <v>1611.692</v>
+        <v>1657.934</v>
       </c>
       <c r="F78">
-        <v>3514.392</v>
+        <v>3560.634</v>
       </c>
       <c r="G78">
         <v>115.4</v>
@@ -7668,37 +7668,37 @@
         <v>444.4</v>
       </c>
       <c r="M78">
-        <v>515.9127456</v>
+        <v>522.7010712</v>
       </c>
       <c r="N78">
-        <v>-71.51274560000002</v>
+        <v>-78.30107120000002</v>
       </c>
       <c r="O78">
-        <v>-21.45382368</v>
+        <v>-23.49032136000001</v>
       </c>
       <c r="P78">
-        <v>-50.05892192000002</v>
+        <v>-54.81074984000001</v>
       </c>
       <c r="Q78">
-        <v>257.94107808</v>
+        <v>253.18925016</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3513402492306325</v>
+        <v>0.364624607892834</v>
       </c>
       <c r="T78">
-        <v>2.130361835953956</v>
+        <v>2.222986263604128</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2584157905324679</v>
+        <v>0.2550597413047735</v>
       </c>
       <c r="W78">
-        <v>0.1088645619498337</v>
+        <v>0.1093572299764593</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8613859684415597</v>
+        <v>0.8501991376825784</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7714,22 +7714,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1680687268972254</v>
+        <v>0.1690787268972255</v>
       </c>
       <c r="C79">
-        <v>185.5997362052804</v>
+        <v>109.6109813038875</v>
       </c>
       <c r="D79">
-        <v>3630.83373620528</v>
+        <v>3601.086981303888</v>
       </c>
       <c r="E79">
-        <v>1657.934</v>
+        <v>1704.176</v>
       </c>
       <c r="F79">
-        <v>3560.634</v>
+        <v>3606.876</v>
       </c>
       <c r="G79">
         <v>115.4</v>
@@ -7750,37 +7750,37 @@
         <v>444.4</v>
       </c>
       <c r="M79">
-        <v>522.7010712</v>
+        <v>529.4893968000001</v>
       </c>
       <c r="N79">
-        <v>-78.30107120000002</v>
+        <v>-85.08939680000015</v>
       </c>
       <c r="O79">
-        <v>-23.49032136000001</v>
+        <v>-25.52681904000004</v>
       </c>
       <c r="P79">
-        <v>-54.81074984000001</v>
+        <v>-59.5625777600001</v>
       </c>
       <c r="Q79">
-        <v>253.18925016</v>
+        <v>248.4374222399999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.364624607892834</v>
+        <v>0.3791166355243265</v>
       </c>
       <c r="T79">
-        <v>2.222986263604128</v>
+        <v>2.324031093767953</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2550597413047735</v>
+        <v>0.2517897446213789</v>
       </c>
       <c r="W79">
-        <v>0.1093572299764593</v>
+        <v>0.1098372654895816</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8501991376825784</v>
+        <v>0.8392991487379297</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7796,22 +7796,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1690787268972255</v>
+        <v>0.1700887268972254</v>
       </c>
       <c r="C80">
-        <v>109.6109813038875</v>
+        <v>34.10568493007986</v>
       </c>
       <c r="D80">
-        <v>3601.086981303888</v>
+        <v>3571.82368493008</v>
       </c>
       <c r="E80">
-        <v>1704.176</v>
+        <v>1750.418</v>
       </c>
       <c r="F80">
-        <v>3606.876</v>
+        <v>3653.118</v>
       </c>
       <c r="G80">
         <v>115.4</v>
@@ -7832,37 +7832,37 @@
         <v>444.4</v>
       </c>
       <c r="M80">
-        <v>529.4893968000001</v>
+        <v>536.2777224</v>
       </c>
       <c r="N80">
-        <v>-85.08939680000015</v>
+        <v>-91.87772240000004</v>
       </c>
       <c r="O80">
-        <v>-25.52681904000004</v>
+        <v>-27.56331672000001</v>
       </c>
       <c r="P80">
-        <v>-59.5625777600001</v>
+        <v>-64.31440568000002</v>
       </c>
       <c r="Q80">
-        <v>248.4374222399999</v>
+        <v>243.68559432</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3791166355243265</v>
+        <v>0.39498885626358</v>
       </c>
       <c r="T80">
-        <v>2.324031093767953</v>
+        <v>2.434699241090236</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2517897446213789</v>
+        <v>0.2486025326641463</v>
       </c>
       <c r="W80">
-        <v>0.1098372654895816</v>
+        <v>0.1103051482049033</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8392991487379297</v>
+        <v>0.8286751088804877</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7878,22 +7878,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1700887268972254</v>
+        <v>0.1710987268972254</v>
       </c>
       <c r="C81">
-        <v>34.10568493007986</v>
+        <v>-40.92784401129938</v>
       </c>
       <c r="D81">
-        <v>3571.82368493008</v>
+        <v>3543.032155988701</v>
       </c>
       <c r="E81">
-        <v>1750.418</v>
+        <v>1796.66</v>
       </c>
       <c r="F81">
-        <v>3653.118</v>
+        <v>3699.36</v>
       </c>
       <c r="G81">
         <v>115.4</v>
@@ -7914,37 +7914,37 @@
         <v>444.4</v>
       </c>
       <c r="M81">
-        <v>536.2777224</v>
+        <v>543.066048</v>
       </c>
       <c r="N81">
-        <v>-91.87772240000004</v>
+        <v>-98.66604800000005</v>
       </c>
       <c r="O81">
-        <v>-27.56331672000001</v>
+        <v>-29.59981440000001</v>
       </c>
       <c r="P81">
-        <v>-64.31440568000002</v>
+        <v>-69.06623360000003</v>
       </c>
       <c r="Q81">
-        <v>243.68559432</v>
+        <v>238.9337664</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.39498885626358</v>
+        <v>0.4124482990767591</v>
       </c>
       <c r="T81">
-        <v>2.434699241090236</v>
+        <v>2.556434203144748</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2486025326641463</v>
+        <v>0.2454950010058445</v>
       </c>
       <c r="W81">
-        <v>0.1103051482049033</v>
+        <v>0.110761333852342</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8286751088804877</v>
+        <v>0.8183166700194816</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7960,22 +7960,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1710987268972254</v>
+        <v>0.1721087268972255</v>
       </c>
       <c r="C82">
-        <v>-40.92784401129938</v>
+        <v>-115.5009226742991</v>
       </c>
       <c r="D82">
-        <v>3543.032155988701</v>
+        <v>3514.701077325701</v>
       </c>
       <c r="E82">
-        <v>1796.66</v>
+        <v>1842.902</v>
       </c>
       <c r="F82">
-        <v>3699.36</v>
+        <v>3745.602</v>
       </c>
       <c r="G82">
         <v>115.4</v>
@@ -7996,37 +7996,37 @@
         <v>444.4</v>
       </c>
       <c r="M82">
-        <v>543.066048</v>
+        <v>549.8543736000001</v>
       </c>
       <c r="N82">
-        <v>-98.66604800000005</v>
+        <v>-105.4543736000002</v>
       </c>
       <c r="O82">
-        <v>-29.59981440000001</v>
+        <v>-31.63631208000005</v>
       </c>
       <c r="P82">
-        <v>-69.06623360000003</v>
+        <v>-73.81806152000011</v>
       </c>
       <c r="Q82">
-        <v>238.9337664</v>
+        <v>234.1819384799999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4124482990767591</v>
+        <v>0.4317455779755359</v>
       </c>
       <c r="T82">
-        <v>2.556434203144748</v>
+        <v>2.690983371731314</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2454950010058445</v>
+        <v>0.2424641985242908</v>
       </c>
       <c r="W82">
-        <v>0.110761333852342</v>
+        <v>0.1112062556566341</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8183166700194816</v>
+        <v>0.8082139950809692</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8042,22 +8042,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1721087268972255</v>
+        <v>0.2222182078948943</v>
       </c>
       <c r="C83">
-        <v>-115.5009226742991</v>
+        <v>-1160.051708078503</v>
       </c>
       <c r="D83">
-        <v>3514.701077325701</v>
+        <v>2516.392291921497</v>
       </c>
       <c r="E83">
-        <v>1842.902</v>
+        <v>1889.144</v>
       </c>
       <c r="F83">
-        <v>3745.602</v>
+        <v>3791.844</v>
       </c>
       <c r="G83">
         <v>115.4</v>
@@ -8078,45 +8078,45 @@
         <v>444.4</v>
       </c>
       <c r="M83">
-        <v>549.8543736000001</v>
+        <v>761.4022752000001</v>
       </c>
       <c r="N83">
-        <v>-105.4543736000002</v>
+        <v>-317.0022752000001</v>
       </c>
       <c r="O83">
-        <v>-31.63631208000005</v>
+        <v>-95.10068256000002</v>
       </c>
       <c r="P83">
-        <v>-73.81806152000011</v>
+        <v>-221.9015926400001</v>
       </c>
       <c r="Q83">
-        <v>234.1819384799999</v>
+        <v>86.09840735999992</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4317455779755359</v>
+        <v>0.4799618934056705</v>
       </c>
       <c r="T83">
-        <v>2.690983371731314</v>
+        <v>3.027168861274268</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.2424641985242908</v>
+        <v>0.1750979795338547</v>
       </c>
       <c r="W83">
-        <v>0.1112062556566341</v>
+        <v>0.165640325709602</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8082139950809692</v>
+        <v>0.5836599317795156</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8124,22 +8124,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2222182078948943</v>
+        <v>0.2237682078948943</v>
       </c>
       <c r="C84">
-        <v>-1160.051708078503</v>
+        <v>-1228.210027283009</v>
       </c>
       <c r="D84">
-        <v>2516.392291921497</v>
+        <v>2494.475972716991</v>
       </c>
       <c r="E84">
-        <v>1889.144</v>
+        <v>1935.386</v>
       </c>
       <c r="F84">
-        <v>3791.844</v>
+        <v>3838.086</v>
       </c>
       <c r="G84">
         <v>115.4</v>
@@ -8160,37 +8160,37 @@
         <v>444.4</v>
       </c>
       <c r="M84">
-        <v>761.4022752000001</v>
+        <v>770.6876688000001</v>
       </c>
       <c r="N84">
-        <v>-317.0022752000001</v>
+        <v>-326.2876688000001</v>
       </c>
       <c r="O84">
-        <v>-95.10068256000002</v>
+        <v>-97.88630064000003</v>
       </c>
       <c r="P84">
-        <v>-221.9015926400001</v>
+        <v>-228.4013681600001</v>
       </c>
       <c r="Q84">
-        <v>86.09840735999992</v>
+        <v>79.59863183999991</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4799618934056705</v>
+        <v>0.5055008283118864</v>
       </c>
       <c r="T84">
-        <v>3.027168861274268</v>
+        <v>3.205237617819814</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1750979795338547</v>
+        <v>0.1729883653226034</v>
       </c>
       <c r="W84">
-        <v>0.165640325709602</v>
+        <v>0.1660639362432212</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5836599317795156</v>
+        <v>0.5766278844086781</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8206,22 +8206,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2237682078948943</v>
+        <v>0.2253182078948943</v>
       </c>
       <c r="C85">
-        <v>-1228.210027283009</v>
+        <v>-1295.989885771297</v>
       </c>
       <c r="D85">
-        <v>2494.475972716991</v>
+        <v>2472.938114228703</v>
       </c>
       <c r="E85">
-        <v>1935.386</v>
+        <v>1981.628</v>
       </c>
       <c r="F85">
-        <v>3838.086</v>
+        <v>3884.328</v>
       </c>
       <c r="G85">
         <v>115.4</v>
@@ -8242,37 +8242,37 @@
         <v>444.4</v>
       </c>
       <c r="M85">
-        <v>770.6876688000001</v>
+        <v>779.9730624000001</v>
       </c>
       <c r="N85">
-        <v>-326.2876688000001</v>
+        <v>-335.5730624000001</v>
       </c>
       <c r="O85">
-        <v>-97.88630064000003</v>
+        <v>-100.67191872</v>
       </c>
       <c r="P85">
-        <v>-228.4013681600001</v>
+        <v>-234.9011436800001</v>
       </c>
       <c r="Q85">
-        <v>79.59863183999991</v>
+        <v>73.0988563199999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5055008283118864</v>
+        <v>0.5342321300813794</v>
       </c>
       <c r="T85">
-        <v>3.205237617819814</v>
+        <v>3.405564968933553</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1729883653226034</v>
+        <v>0.1709289800211438</v>
       </c>
       <c r="W85">
-        <v>0.1660639362432212</v>
+        <v>0.1664774608117543</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5766278844086781</v>
+        <v>0.5697632667371462</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8288,22 +8288,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2253182078948943</v>
+        <v>0.2268682078948943</v>
       </c>
       <c r="C86">
-        <v>-1295.989885771296</v>
+        <v>-1363.401002766586</v>
       </c>
       <c r="D86">
-        <v>2472.938114228703</v>
+        <v>2451.768997233413</v>
       </c>
       <c r="E86">
-        <v>1981.627999999999</v>
+        <v>2027.87</v>
       </c>
       <c r="F86">
-        <v>3884.328</v>
+        <v>3930.57</v>
       </c>
       <c r="G86">
         <v>115.4</v>
@@ -8324,37 +8324,37 @@
         <v>444.4</v>
       </c>
       <c r="M86">
-        <v>779.9730623999999</v>
+        <v>789.2584559999999</v>
       </c>
       <c r="N86">
-        <v>-335.5730623999999</v>
+        <v>-344.8584559999999</v>
       </c>
       <c r="O86">
-        <v>-100.67191872</v>
+        <v>-103.4575368</v>
       </c>
       <c r="P86">
-        <v>-234.90114368</v>
+        <v>-241.4009192</v>
       </c>
       <c r="Q86">
-        <v>73.09885632000004</v>
+        <v>66.59908080000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.534232130081379</v>
+        <v>0.5667942720868042</v>
       </c>
       <c r="T86">
-        <v>3.40556496893355</v>
+        <v>3.63260263352912</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1709289800211439</v>
+        <v>0.1689180508444245</v>
       </c>
       <c r="W86">
-        <v>0.1664774608117543</v>
+        <v>0.1668812553904395</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5697632667371463</v>
+        <v>0.5630601694814151</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8370,22 +8370,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2268682078948943</v>
+        <v>0.2284182078948943</v>
       </c>
       <c r="C87">
-        <v>-1363.401002766586</v>
+        <v>-1430.452767518516</v>
       </c>
       <c r="D87">
-        <v>2451.768997233413</v>
+        <v>2430.959232481483</v>
       </c>
       <c r="E87">
-        <v>2027.87</v>
+        <v>2074.112</v>
       </c>
       <c r="F87">
-        <v>3930.57</v>
+        <v>3976.812</v>
       </c>
       <c r="G87">
         <v>115.4</v>
@@ -8406,37 +8406,37 @@
         <v>444.4</v>
       </c>
       <c r="M87">
-        <v>789.2584559999999</v>
+        <v>798.5438496</v>
       </c>
       <c r="N87">
-        <v>-344.8584559999999</v>
+        <v>-354.1438496000001</v>
       </c>
       <c r="O87">
-        <v>-103.4575368</v>
+        <v>-106.24315488</v>
       </c>
       <c r="P87">
-        <v>-241.4009192</v>
+        <v>-247.90069472</v>
       </c>
       <c r="Q87">
-        <v>66.59908080000002</v>
+        <v>60.09930527999995</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5667942720868042</v>
+        <v>0.6040081486644331</v>
       </c>
       <c r="T87">
-        <v>3.63260263352912</v>
+        <v>3.892074250209772</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1689180508444245</v>
+        <v>0.1669538874625126</v>
       </c>
       <c r="W87">
-        <v>0.1668812553904395</v>
+        <v>0.1672756593975275</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5630601694814151</v>
+        <v>0.5565129582083753</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8452,22 +8452,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2284182078948943</v>
+        <v>0.2299682078948943</v>
       </c>
       <c r="C88">
-        <v>-1430.452767518516</v>
+        <v>-1497.154253188794</v>
       </c>
       <c r="D88">
-        <v>2430.959232481483</v>
+        <v>2410.499746811205</v>
       </c>
       <c r="E88">
-        <v>2074.112</v>
+        <v>2120.353999999999</v>
       </c>
       <c r="F88">
-        <v>3976.812</v>
+        <v>4023.054</v>
       </c>
       <c r="G88">
         <v>115.4</v>
@@ -8488,37 +8488,37 @@
         <v>444.4</v>
       </c>
       <c r="M88">
-        <v>798.5438496</v>
+        <v>807.8292432</v>
       </c>
       <c r="N88">
-        <v>-354.1438496000001</v>
+        <v>-363.4292432</v>
       </c>
       <c r="O88">
-        <v>-106.24315488</v>
+        <v>-109.02877296</v>
       </c>
       <c r="P88">
-        <v>-247.90069472</v>
+        <v>-254.40047024</v>
       </c>
       <c r="Q88">
-        <v>60.09930527999995</v>
+        <v>53.59952976</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6040081486644331</v>
+        <v>0.6469472370232358</v>
       </c>
       <c r="T88">
-        <v>3.892074250209772</v>
+        <v>4.191464577148985</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1669538874625126</v>
+        <v>0.1650348772617941</v>
       </c>
       <c r="W88">
-        <v>0.1672756593975275</v>
+        <v>0.1676609966458318</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5565129582083753</v>
+        <v>0.5501162575393136</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8534,22 +8534,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2299682078948943</v>
+        <v>0.2315182078948943</v>
       </c>
       <c r="C89">
-        <v>-1497.154253188794</v>
+        <v>-1563.51423004151</v>
       </c>
       <c r="D89">
-        <v>2410.499746811205</v>
+        <v>2390.381769958489</v>
       </c>
       <c r="E89">
-        <v>2120.353999999999</v>
+        <v>2166.596</v>
       </c>
       <c r="F89">
-        <v>4023.054</v>
+        <v>4069.296</v>
       </c>
       <c r="G89">
         <v>115.4</v>
@@ -8570,37 +8570,37 @@
         <v>444.4</v>
       </c>
       <c r="M89">
-        <v>807.8292432</v>
+        <v>817.1146368</v>
       </c>
       <c r="N89">
-        <v>-363.4292432</v>
+        <v>-372.7146368</v>
       </c>
       <c r="O89">
-        <v>-109.02877296</v>
+        <v>-111.81439104</v>
       </c>
       <c r="P89">
-        <v>-254.40047024</v>
+        <v>-260.90024576</v>
       </c>
       <c r="Q89">
-        <v>53.59952976</v>
+        <v>47.09975423999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6469472370232358</v>
+        <v>0.6970428401085056</v>
       </c>
       <c r="T89">
-        <v>4.191464577148985</v>
+        <v>4.540753291911402</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1650348772617941</v>
+        <v>0.1631594809292737</v>
       </c>
       <c r="W89">
-        <v>0.1676609966458318</v>
+        <v>0.1680375762294019</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5501162575393136</v>
+        <v>0.5438649364309123</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8616,22 +8616,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2315182078948943</v>
+        <v>0.2330682078948943</v>
       </c>
       <c r="C90">
-        <v>-1563.51423004151</v>
+        <v>-1629.541177978402</v>
       </c>
       <c r="D90">
-        <v>2390.381769958489</v>
+        <v>2370.596822021597</v>
       </c>
       <c r="E90">
-        <v>2166.596</v>
+        <v>2212.838</v>
       </c>
       <c r="F90">
-        <v>4069.296</v>
+        <v>4115.538</v>
       </c>
       <c r="G90">
         <v>115.4</v>
@@ -8652,37 +8652,37 @@
         <v>444.4</v>
       </c>
       <c r="M90">
-        <v>817.1146368</v>
+        <v>826.4000304</v>
       </c>
       <c r="N90">
-        <v>-372.7146368</v>
+        <v>-382.0000304</v>
       </c>
       <c r="O90">
-        <v>-111.81439104</v>
+        <v>-114.60000912</v>
       </c>
       <c r="P90">
-        <v>-260.90024576</v>
+        <v>-267.40002128</v>
       </c>
       <c r="Q90">
-        <v>47.09975423999998</v>
+        <v>40.59997871999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6970428401085056</v>
+        <v>0.7562467346638241</v>
       </c>
       <c r="T90">
-        <v>4.540753291911402</v>
+        <v>4.953549045721529</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1631594809292737</v>
+        <v>0.1613262283345628</v>
       </c>
       <c r="W90">
-        <v>0.1680375762294019</v>
+        <v>0.1684056933504198</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5438649364309123</v>
+        <v>0.5377540944485425</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8698,22 +8698,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2330682078948943</v>
+        <v>0.2346182078948943</v>
       </c>
       <c r="C91">
-        <v>-1629.541177978402</v>
+        <v>-1695.243298456714</v>
       </c>
       <c r="D91">
-        <v>2370.596822021597</v>
+        <v>2351.136701543285</v>
       </c>
       <c r="E91">
-        <v>2212.838</v>
+        <v>2259.08</v>
       </c>
       <c r="F91">
-        <v>4115.538</v>
+        <v>4161.78</v>
       </c>
       <c r="G91">
         <v>115.4</v>
@@ -8734,37 +8734,37 @@
         <v>444.4</v>
       </c>
       <c r="M91">
-        <v>826.4000304</v>
+        <v>835.685424</v>
       </c>
       <c r="N91">
-        <v>-382.0000304</v>
+        <v>-391.285424</v>
       </c>
       <c r="O91">
-        <v>-114.60000912</v>
+        <v>-117.3856272</v>
       </c>
       <c r="P91">
-        <v>-267.40002128</v>
+        <v>-273.8997968</v>
       </c>
       <c r="Q91">
-        <v>40.59997871999997</v>
+        <v>34.10020319999995</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7562467346638241</v>
+        <v>0.8272914081302066</v>
       </c>
       <c r="T91">
-        <v>4.953549045721529</v>
+        <v>5.448903950293682</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1613262283345628</v>
+        <v>0.1595337146864009</v>
       </c>
       <c r="W91">
-        <v>0.1684056933504198</v>
+        <v>0.1687656300909707</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5377540944485425</v>
+        <v>0.5317790489546698</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8780,22 +8780,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2346182078948943</v>
+        <v>0.2361682078948943</v>
       </c>
       <c r="C92">
-        <v>-1695.243298456714</v>
+        <v>-1760.628525824827</v>
       </c>
       <c r="D92">
-        <v>2351.136701543285</v>
+        <v>2331.993474175173</v>
       </c>
       <c r="E92">
-        <v>2259.08</v>
+        <v>2305.322</v>
       </c>
       <c r="F92">
-        <v>4161.78</v>
+        <v>4208.022</v>
       </c>
       <c r="G92">
         <v>115.4</v>
@@ -8816,37 +8816,37 @@
         <v>444.4</v>
       </c>
       <c r="M92">
-        <v>835.685424</v>
+        <v>844.9708176</v>
       </c>
       <c r="N92">
-        <v>-391.285424</v>
+        <v>-400.5708176000001</v>
       </c>
       <c r="O92">
-        <v>-117.3856272</v>
+        <v>-120.17124528</v>
       </c>
       <c r="P92">
-        <v>-273.8997968</v>
+        <v>-280.3995723200001</v>
       </c>
       <c r="Q92">
-        <v>34.10020319999995</v>
+        <v>27.60042767999994</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8272914081302066</v>
+        <v>0.9141237868113409</v>
       </c>
       <c r="T92">
-        <v>5.448903950293682</v>
+        <v>6.054337722548537</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1595337146864009</v>
+        <v>0.1577805969425943</v>
       </c>
       <c r="W92">
-        <v>0.1687656300909707</v>
+        <v>0.1691176561339271</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5317790489546698</v>
+        <v>0.5259353231419811</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8862,22 +8862,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2361682078948943</v>
+        <v>0.2377182078948943</v>
       </c>
       <c r="C93">
-        <v>-1760.628525824827</v>
+        <v>-1825.704538108597</v>
       </c>
       <c r="D93">
-        <v>2331.993474175173</v>
+        <v>2313.159461891403</v>
       </c>
       <c r="E93">
-        <v>2305.322</v>
+        <v>2351.564</v>
       </c>
       <c r="F93">
-        <v>4208.022</v>
+        <v>4254.264</v>
       </c>
       <c r="G93">
         <v>115.4</v>
@@ -8898,37 +8898,37 @@
         <v>444.4</v>
       </c>
       <c r="M93">
-        <v>844.9708176</v>
+        <v>854.2562112000001</v>
       </c>
       <c r="N93">
-        <v>-400.5708176000001</v>
+        <v>-409.8562112000001</v>
       </c>
       <c r="O93">
-        <v>-120.17124528</v>
+        <v>-122.95686336</v>
       </c>
       <c r="P93">
-        <v>-280.3995723200001</v>
+        <v>-286.8993478400001</v>
       </c>
       <c r="Q93">
-        <v>27.60042767999994</v>
+        <v>21.10065215999992</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9141237868113409</v>
+        <v>1.022664260162759</v>
       </c>
       <c r="T93">
-        <v>6.054337722548537</v>
+        <v>6.811129937867106</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1577805969425943</v>
+        <v>0.1560655904540879</v>
       </c>
       <c r="W93">
-        <v>0.1691176561339271</v>
+        <v>0.1694620294368192</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5259353231419811</v>
+        <v>0.5202186348469595</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8944,22 +8944,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2377182078948943</v>
+        <v>0.2392682078948943</v>
       </c>
       <c r="C94">
-        <v>-1825.704538108597</v>
+        <v>-1890.478767279188</v>
       </c>
       <c r="D94">
-        <v>2313.159461891403</v>
+        <v>2294.627232720812</v>
       </c>
       <c r="E94">
-        <v>2351.564</v>
+        <v>2397.806</v>
       </c>
       <c r="F94">
-        <v>4254.264</v>
+        <v>4300.506</v>
       </c>
       <c r="G94">
         <v>115.4</v>
@@ -8980,37 +8980,37 @@
         <v>444.4</v>
       </c>
       <c r="M94">
-        <v>854.2562112000001</v>
+        <v>863.5416048000001</v>
       </c>
       <c r="N94">
-        <v>-409.8562112000001</v>
+        <v>-419.1416048000001</v>
       </c>
       <c r="O94">
-        <v>-122.95686336</v>
+        <v>-125.74248144</v>
       </c>
       <c r="P94">
-        <v>-286.8993478400001</v>
+        <v>-293.3991233600001</v>
       </c>
       <c r="Q94">
-        <v>21.10065215999992</v>
+        <v>14.60087663999991</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.022664260162759</v>
+        <v>1.162216297328867</v>
       </c>
       <c r="T94">
-        <v>6.811129937867106</v>
+        <v>7.784148500419549</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1560655904540879</v>
+        <v>0.1543874658255493</v>
       </c>
       <c r="W94">
-        <v>0.1694620294368192</v>
+        <v>0.1697989968622297</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5202186348469595</v>
+        <v>0.5146248860851643</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9026,22 +9026,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2392682078948943</v>
+        <v>0.2408182078948943</v>
       </c>
       <c r="C95">
-        <v>-1890.478767279188</v>
+        <v>-1954.958409031256</v>
       </c>
       <c r="D95">
-        <v>2294.627232720812</v>
+        <v>2276.389590968745</v>
       </c>
       <c r="E95">
-        <v>2397.806</v>
+        <v>2444.048000000001</v>
       </c>
       <c r="F95">
-        <v>4300.506</v>
+        <v>4346.748000000001</v>
       </c>
       <c r="G95">
         <v>115.4</v>
@@ -9062,37 +9062,37 @@
         <v>444.4</v>
       </c>
       <c r="M95">
-        <v>863.5416048000001</v>
+        <v>872.8269984000001</v>
       </c>
       <c r="N95">
-        <v>-419.1416048000001</v>
+        <v>-428.4269984000001</v>
       </c>
       <c r="O95">
-        <v>-125.74248144</v>
+        <v>-128.52809952</v>
       </c>
       <c r="P95">
-        <v>-293.3991233600001</v>
+        <v>-299.89889888</v>
       </c>
       <c r="Q95">
-        <v>14.60087663999991</v>
+        <v>8.101101119999953</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.162216297328867</v>
+        <v>1.348285680217012</v>
       </c>
       <c r="T95">
-        <v>7.784148500419549</v>
+        <v>9.081506583822812</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1543874658255493</v>
+        <v>0.1527450459763413</v>
       </c>
       <c r="W95">
-        <v>0.1697989968622297</v>
+        <v>0.1701287947679507</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5146248860851643</v>
+        <v>0.509150153254471</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9108,22 +9108,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2408182078948943</v>
+        <v>0.2423682078948943</v>
       </c>
       <c r="C96">
-        <v>-1954.958409031256</v>
+        <v>-2019.150432098506</v>
       </c>
       <c r="D96">
-        <v>2276.389590968745</v>
+        <v>2258.439567901494</v>
       </c>
       <c r="E96">
-        <v>2444.048000000001</v>
+        <v>2490.29</v>
       </c>
       <c r="F96">
-        <v>4346.748000000001</v>
+        <v>4392.99</v>
       </c>
       <c r="G96">
         <v>115.4</v>
@@ -9144,37 +9144,37 @@
         <v>444.4</v>
       </c>
       <c r="M96">
-        <v>872.8269984000001</v>
+        <v>882.112392</v>
       </c>
       <c r="N96">
-        <v>-428.4269984000001</v>
+        <v>-437.712392</v>
       </c>
       <c r="O96">
-        <v>-128.52809952</v>
+        <v>-131.3137176</v>
       </c>
       <c r="P96">
-        <v>-299.89889888</v>
+        <v>-306.3986744</v>
       </c>
       <c r="Q96">
-        <v>8.101101119999953</v>
+        <v>1.601325599999996</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.348285680217012</v>
+        <v>1.608782816260415</v>
       </c>
       <c r="T96">
-        <v>9.081506583822812</v>
+        <v>10.89780790058738</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1527450459763413</v>
+        <v>0.1511372033871167</v>
       </c>
       <c r="W96">
-        <v>0.1701287947679507</v>
+        <v>0.170451649559867</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.509150153254471</v>
+        <v>0.5037906779570556</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9190,22 +9190,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2423682078948943</v>
+        <v>0.2794629266903285</v>
       </c>
       <c r="C97">
-        <v>-2019.150432098506</v>
+        <v>-2423.926761332581</v>
       </c>
       <c r="D97">
-        <v>2258.439567901494</v>
+        <v>1899.905238667419</v>
       </c>
       <c r="E97">
-        <v>2490.29</v>
+        <v>2536.532</v>
       </c>
       <c r="F97">
-        <v>4392.99</v>
+        <v>4439.232</v>
       </c>
       <c r="G97">
         <v>115.4</v>
@@ -9226,45 +9226,45 @@
         <v>444.4</v>
       </c>
       <c r="M97">
-        <v>882.112392</v>
+        <v>1046.7709056</v>
       </c>
       <c r="N97">
-        <v>-437.712392</v>
+        <v>-602.3709056000001</v>
       </c>
       <c r="O97">
-        <v>-131.3137176</v>
+        <v>-180.71127168</v>
       </c>
       <c r="P97">
-        <v>-306.3986744</v>
+        <v>-421.6596339200001</v>
       </c>
       <c r="Q97">
-        <v>1.601325599999996</v>
+        <v>-113.6596339200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.608782816260415</v>
+        <v>2.048146490211374</v>
       </c>
       <c r="T97">
-        <v>10.89780790058738</v>
+        <v>13.96124587789659</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1511372033871167</v>
+        <v>0.1273631119156699</v>
       </c>
       <c r="W97">
-        <v>0.170451649559867</v>
+        <v>0.205767778210285</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5037906779570556</v>
+        <v>0.4245437063855665</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9272,22 +9272,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2794629266903285</v>
+        <v>0.2813629266903285</v>
       </c>
       <c r="C98">
-        <v>-2423.926761332581</v>
+        <v>-2485.492989147994</v>
       </c>
       <c r="D98">
-        <v>1899.905238667419</v>
+        <v>1884.581010852005</v>
       </c>
       <c r="E98">
-        <v>2536.532</v>
+        <v>2582.773999999999</v>
       </c>
       <c r="F98">
-        <v>4439.232</v>
+        <v>4485.473999999999</v>
       </c>
       <c r="G98">
         <v>115.4</v>
@@ -9308,37 +9308,37 @@
         <v>444.4</v>
       </c>
       <c r="M98">
-        <v>1046.7709056</v>
+        <v>1057.6747692</v>
       </c>
       <c r="N98">
-        <v>-602.3709056000001</v>
+        <v>-613.2747691999999</v>
       </c>
       <c r="O98">
-        <v>-180.71127168</v>
+        <v>-183.98243076</v>
       </c>
       <c r="P98">
-        <v>-421.6596339200001</v>
+        <v>-429.29233844</v>
       </c>
       <c r="Q98">
-        <v>-113.6596339200001</v>
+        <v>-121.29233844</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.048146490211369</v>
+        <v>2.715595320281826</v>
       </c>
       <c r="T98">
-        <v>13.96124587789655</v>
+        <v>18.61499450386207</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1273631119156699</v>
+        <v>0.1260500901433435</v>
       </c>
       <c r="W98">
-        <v>0.205767778210285</v>
+        <v>0.2060773887441996</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4245437063855665</v>
+        <v>0.4201669671444782</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9354,22 +9354,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2813629266903285</v>
+        <v>0.2832629266903285</v>
       </c>
       <c r="C99">
-        <v>-2485.492989147994</v>
+        <v>-2546.813991039049</v>
       </c>
       <c r="D99">
-        <v>1884.581010852005</v>
+        <v>1869.502008960951</v>
       </c>
       <c r="E99">
-        <v>2582.773999999999</v>
+        <v>2629.016</v>
       </c>
       <c r="F99">
-        <v>4485.473999999999</v>
+        <v>4531.715999999999</v>
       </c>
       <c r="G99">
         <v>115.4</v>
@@ -9390,37 +9390,37 @@
         <v>444.4</v>
       </c>
       <c r="M99">
-        <v>1057.6747692</v>
+        <v>1068.5786328</v>
       </c>
       <c r="N99">
-        <v>-613.2747691999999</v>
+        <v>-624.1786327999999</v>
       </c>
       <c r="O99">
-        <v>-183.98243076</v>
+        <v>-187.25358984</v>
       </c>
       <c r="P99">
-        <v>-429.29233844</v>
+        <v>-436.9250429599999</v>
       </c>
       <c r="Q99">
-        <v>-121.29233844</v>
+        <v>-128.9250429599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.715595320281826</v>
+        <v>4.050492980422739</v>
       </c>
       <c r="T99">
-        <v>18.61499450386207</v>
+        <v>27.92249175579311</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1260500901433435</v>
+        <v>0.1247638647337175</v>
       </c>
       <c r="W99">
-        <v>0.2060773887441996</v>
+        <v>0.2063806806957894</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4201669671444782</v>
+        <v>0.4158795491123918</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9436,22 +9436,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2832629266903285</v>
+        <v>0.2851629266903285</v>
       </c>
       <c r="C100">
-        <v>-2546.813991039049</v>
+        <v>-2607.895606622548</v>
       </c>
       <c r="D100">
-        <v>1869.502008960951</v>
+        <v>1854.662393377452</v>
       </c>
       <c r="E100">
-        <v>2629.016</v>
+        <v>2675.258</v>
       </c>
       <c r="F100">
-        <v>4531.715999999999</v>
+        <v>4577.958</v>
       </c>
       <c r="G100">
         <v>115.4</v>
@@ -9472,37 +9472,37 @@
         <v>444.4</v>
       </c>
       <c r="M100">
-        <v>1068.5786328</v>
+        <v>1079.4824964</v>
       </c>
       <c r="N100">
-        <v>-624.1786327999999</v>
+        <v>-635.0824964</v>
       </c>
       <c r="O100">
-        <v>-187.25358984</v>
+        <v>-190.52474892</v>
       </c>
       <c r="P100">
-        <v>-436.9250429599999</v>
+        <v>-444.55774748</v>
       </c>
       <c r="Q100">
-        <v>-128.9250429599999</v>
+        <v>-136.55774748</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.050492980422739</v>
+        <v>8.055185960845478</v>
       </c>
       <c r="T100">
-        <v>27.92249175579311</v>
+        <v>55.84498351158621</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1247638647337175</v>
+        <v>0.1235036236758012</v>
       </c>
       <c r="W100">
-        <v>0.2063806806957894</v>
+        <v>0.2066778455372461</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9510,91 +9510,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4158795491123918</v>
+        <v>0.4116787455860039</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2851629266903285</v>
-      </c>
-      <c r="C101">
-        <v>-2607.895606622548</v>
-      </c>
-      <c r="D101">
-        <v>1854.662393377452</v>
-      </c>
-      <c r="E101">
-        <v>2675.258</v>
-      </c>
-      <c r="F101">
-        <v>4577.958</v>
-      </c>
-      <c r="G101">
-        <v>115.4</v>
-      </c>
-      <c r="H101">
-        <v>2721.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>752.4</v>
-      </c>
-      <c r="K101">
-        <v>308</v>
-      </c>
-      <c r="L101">
-        <v>444.4</v>
-      </c>
-      <c r="M101">
-        <v>1079.4824964</v>
-      </c>
-      <c r="N101">
-        <v>-635.0824964</v>
-      </c>
-      <c r="O101">
-        <v>-190.52474892</v>
-      </c>
-      <c r="P101">
-        <v>-444.55774748</v>
-      </c>
-      <c r="Q101">
-        <v>-136.55774748</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.055185960845478</v>
-      </c>
-      <c r="T101">
-        <v>55.84498351158621</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1235036236758012</v>
-      </c>
-      <c r="W101">
-        <v>0.2066778455372461</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4116787455860039</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
